--- a/data/evaluation/optimized/retrieval_results.xlsx
+++ b/data/evaluation/optimized/retrieval_results.xlsx
@@ -904,12 +904,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：China + 1 战略（多地区混合布局） - Evidence ID: PLUS1_003 Title: 比亚迪 BYD：China + 1 战略（多地区混合布局） Publisher: 凤...</t>
+          <t>比亚迪 BYD：China + 1 战略（多地区混合布局） - Evidence ID: PLUS1_003 Title: 比亚迪 BYD：China + 1 战略（多地区混合布局） Publisher: A...</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>凤凰科技（转路透社）</t>
+          <t>ANTARA（印尼国家通讯社）</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2074,12 +2074,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publi...</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_002 Title: 富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提...</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>路透社（经环球网 / 新浪转载）</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2110,14 +2110,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -2139,12 +2139,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
+          <t>制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_003 Title: 制造业外迁企业（行业层面）：重新评估 / 回流中国（提高中国生产比例） Publi...</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>路透社（经环球网 / 新浪转载）</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2164,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>RELOC_006</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_003 Title: 国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） ...</t>
+          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_006 Title: 蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） Publisher: ...</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>澎湃新闻</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>RELOC_003</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_004 Title: 亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） Publis...</t>
+          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_003 Title: 国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） ...</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>新浪财经</t>
+          <t>澎湃新闻 / 盖世汽车社区</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>RELOC_004</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2315,7 +2315,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_002 Title: 长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局...</t>
+          <t>亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_004 Title: 亿纬锂能 EVE Energy：中国 → 东南亚转移（多地区混合布局） Publis...</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>易车 / 证券之星（投资者互动平台）</t>
+          <t>新浪财经</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2349,11 +2349,11 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2370,17 +2370,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>RELOC_002</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） - Evidence ID: RETURN_002 Title: 富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提...</t>
+          <t>长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_002 Title: 长安汽车 Changan Automobile：中国 → 东南亚转移（多地区混合布局...</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>新浪科技 / 中关村在线</t>
+          <t>易车 / 证券之星（投资者互动平台）</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>RETURN_001</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -6234,26 +6234,26 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -6299,26 +6299,26 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：湿法锂电隔膜产能以中国为主（上海、珠海、无锡等），为全球隔膜龙头。 主要市...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>恩捷股份公告（经东方财富网 / 央广网报道）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RELOC_005</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新增）） - Evidence ID: RETURN_004 Title: 蜂巢能源 SVOLT（欧洲业务）：重新评估 / 回流中国（维持现有海外布局（收缩新...</t>
+          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - Evidence ID: RELOC_005 Title: 欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） Publisher:...</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>36氪 / 财新网</t>
+          <t>东方财富网 / 腾讯新闻</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>PLUS1_005</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -8165,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -8184,26 +8184,26 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>三星电子 Samsung Electronics：China + 1 战略（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：半导体与消费电子产能分布在中国（西安 NAND、苏州封测）、韩国、越南（手...</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>新浪财经 / 东方财富网</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -8249,26 +8249,26 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech：中国 → 东南亚转移（多地区混合布局） - ## 一、决策前状态（Initial Situation） 生产布局：电芯产能集中于中国（合肥、庐江、南京等基地），海外仅有销售与研发。 主要市...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>澎湃新闻 / 盖世汽车社区</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT：中国 → 东南亚转移（多地区混合布局） - ## 三、实际决策（Actual Decision） 决策分类：多地区混合布局 决策内容：在泰国春武里府是拉差市建设电池工厂（模组 PACK +...</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：苹果产品组装以中国大陆为核心，印度、越南为分散地。 主要市场：全球。 供应...</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>澎湃新闻</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O172" t="n">
         <v>1</v>
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -17433,7 +17433,7 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -18555,17 +18555,17 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="C279" t="n">
         <v>8</v>
       </c>
       <c r="D279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -18584,32 +18584,32 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：重新评估 / 回流中国（提高中国生产比例） - ## 一、决策前状态（Initial Situation） 生产布局：苹果产品组装以中国大陆为核心，印度、越南为分散地。 主要市场：全球。 供应...</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>新浪科技 / 中关村在线</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N279" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
       </c>
       <c r="P279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -18620,14 +18620,14 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C280" t="n">
         <v>9</v>
       </c>
       <c r="D280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E280" t="n">
         <v>2</v>
@@ -18649,22 +18649,22 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N280" t="n">
@@ -18674,7 +18674,7 @@
         <v>0</v>
       </c>
       <c r="P280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -18695,7 +18695,7 @@
         <v>1</v>
       </c>
       <c r="E281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -18714,22 +18714,22 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda：中国 → 东南亚转移（多地区混合布局） - ## 二、决策触发（Decision Trigger） 触发类型：tariff_pressure（关税压力） 触发细节：美国对华加征关税及客户'...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>东方财富网 / 腾讯新闻</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N281" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RETURN_001; CASE_001; RETURN_004; RETURN_003; RELOC_006; RELOC_003; RELOC_004; RELOC_002; RETURN_002; RELOC_005</t>
+          <t>RETURN_001; CASE_001; RETURN_004; RETURN_002; RETURN_003; RELOC_006; RELOC_003; RELOC_004; RELOC_002; RELOC_005</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20379,7 +20379,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -20838,7 +20838,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; CASE_003; TRD_003; TRD_001; RETURN_001; RELOC_005</t>
+          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; CASE_003; TRD_003; RETURN_001; TRD_001; RELOC_005</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20919,7 +20919,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; RETURN_001; RELOC_001; TRD_003; RETURN_004</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; RETURN_001; RELOC_001; TRD_003; RELOC_005</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>WH_001; RETURN_001; RETURN_004</t>
+          <t>WH_001; RETURN_001; RELOC_005</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -21081,7 +21081,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; TRD_003; RELOC_003; RELOC_006</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; TRD_003; RELOC_003; RELOC_006</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; RETURN_001; RELOC_005; PLUS1_002; PLUS1_001; PLUS1_005; TRD_003; RETURN_002</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -22325,7 +22325,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001; CASE_003; RELOC_001; CASE_010; WTO_001; RELOC_005</t>
+          <t>TRD_003; WH_002; DOC_001; CASE_002; RETURN_001; CASE_003; RELOC_001; RETURN_002; CASE_010; WTO_001</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">

--- a/data/evaluation/optimized/retrieval_results.xlsx
+++ b/data/evaluation/optimized/retrieval_results.xlsx
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - "Utilization" and "utilized" means the cells and modules will be used or...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1070,14 +1070,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -1099,26 +1099,26 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - "Utilization" and "utilized" means the cells and modules will be used or...</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1164,26 +1164,26 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Some are major trading partners with diversified industrial bases and la...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1330,14 +1330,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -1359,17 +1359,17 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -1395,14 +1395,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2370,14 +2370,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>9</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -2399,17 +2399,17 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Delay in the Suspension of Liquidation and Cash Deposit Requirements (B)...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2435,14 +2435,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>10</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -2464,26 +2464,26 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The cost of not knowing is rising faster than the cost of ﬁnding out, an...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - companies' costs in expanding domestic production capacity while maintai...</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2955,14 +2955,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -2984,17 +2984,17 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - But China-linked exporters gravitate to them because each offers a speci...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -3020,14 +3020,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C40" t="n">
         <v>9</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -3049,17 +3049,17 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - But China-linked exporters gravitate to them because each offers a speci...</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -3085,14 +3085,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -3114,26 +3114,26 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O42" t="n">
         <v>1</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -3355,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3374,26 +3374,26 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Introduction Every year, the United States loses tens of billions of dol...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
@@ -3410,14 +3410,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C46" t="n">
         <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -3439,32 +3439,32 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - If global trade uncertainty continues to intensify and spread, the pract...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3485,7 +3485,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3504,26 +3504,26 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Introduction Every year, the United States loses tens of billions of dol...</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -3540,17 +3540,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>7</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3569,32 +3569,32 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 天孚通信：光引擎垄断者 天孚通信是全球光引擎市场龙头，占据60%以上份额，产品价值占CPO模块的30%-40%。 2025年预计归母净利润18....</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3680,7 +3680,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3699,26 +3699,26 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 天孚通信：光引擎垄断者 天孚通信是全球光引擎市场龙头，占据60%以上份额，产品价值占CPO模块的30%-40%。 2025年预计归母净利润18....</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The Trusted Trade Laboratory: A North American Model for Veriﬁed Trade T...</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>KPMG_001</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3764,26 +3764,26 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - lithium-ion, including separators, whether or not rectangular (including...</t>
+          <t>KPMG 2026 US Supply Chain Survey - Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher:...</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>毕马威（KPMG）</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3978,13 +3978,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
@@ -4024,12 +4024,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -4255,14 +4255,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>8</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>2</v>
@@ -4284,17 +4284,17 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Paul Dominican Republic (Caucedo–Haina) Insulated conductors and cable a...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -4320,14 +4320,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>9</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
@@ -4349,26 +4349,26 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The Trusted Trade Laboratory: A North American Model for Veriﬁed Trade T...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -4414,17 +4414,17 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>BIS_002</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BIS_002</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>One Year Suspension of Expansion of End-User Controls for Affiliates of Certain Listed Entities（关联企业规则暂停一年） - Evidence ID: BIS_002 Title: One Year Suspension of Expansion of End-User...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O64" t="n">
         <v>1</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="O65" t="n">
         <v>1</v>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -4840,14 +4840,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
@@ -4869,26 +4869,26 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The Trusted Trade Laboratory: A North American Model for Veriﬁed Trade T...</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -4905,14 +4905,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>2</v>
@@ -4934,26 +4934,26 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The Trusted Trade Laboratory: A North American Model for Veriﬁed Trade T...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -4999,17 +4999,17 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -5035,14 +5035,14 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>10</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>2</v>
@@ -5064,17 +5064,17 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - (b) The Secretary and the Attorney General shall take all appropriate ac...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Trade Representative has determined to: modify the actions being taken i...</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -5295,14 +5295,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
         <v>2</v>
@@ -5324,17 +5324,17 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5343,13 +5343,13 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -5425,14 +5425,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FR_001</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>6</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
         <v>2</v>
@@ -5454,17 +5454,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
+          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>美国国家档案馆联邦公报办公室</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>出口管制/关税</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5479,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - However, as trade volumes surged, supply chains became more complicated,...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -5620,14 +5620,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>9</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>2</v>
@@ -5649,17 +5649,17 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - - 44 - 序号 管制编码 物项名称及描述 参考商品名称 海关商品编号 单位 乙 酯 （ CAS 2387496-06-0） 基氟磷酸甲酯 N...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - 91. 04 applies to facemasks of textiles, disposable, of China, described...</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -5685,14 +5685,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>10</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>2</v>
@@ -5714,17 +5714,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - (c) This order is not intended to, and does not, create any right or ben...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Current consolidated version: 11/02/2026 ELI: Language BG ES CS DA DE ET...</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O82" t="n">
         <v>1</v>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="O84" t="n">
         <v>1</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
@@ -6058,7 +6058,7 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O86" t="n">
         <v>1</v>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -6188,7 +6188,7 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -6318,7 +6318,7 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -6364,17 +6364,17 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O92" t="n">
         <v>1</v>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
@@ -6660,14 +6660,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>5</v>
       </c>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
         <v>2</v>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6708,13 +6708,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -6725,14 +6725,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>6</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
         <v>2</v>
@@ -6754,32 +6754,32 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -6790,14 +6790,14 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>7</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>2</v>
@@ -6819,17 +6819,17 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -6838,7 +6838,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -6884,26 +6884,26 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -6920,14 +6920,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100" t="n">
         <v>2</v>
@@ -6949,26 +6949,26 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -7014,26 +7014,26 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="O104" t="n">
         <v>1</v>
@@ -7245,17 +7245,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -7274,26 +7274,26 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Lashley, Senior Fellow Don Marshall, Professor Kenisha Chase, Research A...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="O105" t="n">
         <v>1</v>
@@ -7310,17 +7310,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>5</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -7339,26 +7339,26 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Once leaders have defined their objectives, they can choose from a tool ...</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O106" t="n">
         <v>1</v>
@@ -7375,14 +7375,14 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>6</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107" t="n">
         <v>2</v>
@@ -7404,17 +7404,17 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - The United States under President Trump will simply not allow its manufa...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - (b) critical technologies and dual use items as defined in point 1 of Ar...</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - When designing the playbook, the executives asked themselves a series of...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Lashley, Senior Fellow Don Marshall, Professor Kenisha Chase, Research A...</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7484,11 +7484,11 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -7534,26 +7534,26 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -7599,26 +7599,26 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - GLOBAL TRADE OUTLOOK AND STATISTICS - MARCH 2026 40 Bibliography Abbas, ...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - The United States under President Trump will simply not allow its manufa...</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -7664,26 +7664,26 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="O112" t="n">
         <v>1</v>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
@@ -7943,7 +7943,7 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="O115" t="n">
         <v>1</v>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O116" t="n">
         <v>1</v>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -8119,17 +8119,17 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - cn/en/3688253/3689009/4180845/4821853/2023031716595159517. pdf https://w...</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -8249,26 +8249,26 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -8295,7 +8295,7 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -8314,26 +8314,26 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8398,7 +8398,7 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="O122" t="n">
         <v>1</v>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="O123" t="n">
         <v>1</v>
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="O124" t="n">
         <v>1</v>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8589,11 +8589,11 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N125" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="O125" t="n">
         <v>1</v>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8654,11 +8654,11 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
@@ -8675,14 +8675,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
         <v>2</v>
@@ -8704,26 +8704,26 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N127" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>KPMG_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -8834,26 +8834,26 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>KPMG 2026 US Supply Chain Survey - Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher:...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>毕马威（KPMG）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N129" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -8870,17 +8870,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C130" t="n">
         <v>9</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -8899,22 +8899,22 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O132" t="n">
         <v>1</v>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="O133" t="n">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="O135" t="n">
         <v>1</v>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -9354,12 +9354,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -9455,14 +9455,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C139" t="n">
         <v>8</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
         <v>2</v>
@@ -9484,17 +9484,17 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -9549,17 +9549,17 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -9585,14 +9585,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C141" t="n">
         <v>10</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>2</v>
@@ -9614,26 +9614,26 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O143" t="n">
         <v>1</v>
@@ -9893,7 +9893,7 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O145" t="n">
         <v>1</v>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="O146" t="n">
         <v>1</v>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -10040,7 +10040,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -10069,17 +10069,17 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -10105,14 +10105,14 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C149" t="n">
         <v>8</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
         <v>2</v>
@@ -10134,26 +10134,26 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - An electric vehicle (EV) battery can pass through a Chinese cathode supp...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N149" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -10170,14 +10170,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C150" t="n">
         <v>9</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
         <v>2</v>
@@ -10199,26 +10199,26 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - An electric vehicle (EV) battery can pass through a Chinese cathode supp...</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -10283,7 +10283,7 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="O152" t="n">
         <v>1</v>
@@ -10365,14 +10365,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
@@ -10394,32 +10394,32 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="O153" t="n">
         <v>1</v>
       </c>
       <c r="P153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -10430,14 +10430,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C154" t="n">
         <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
         <v>2</v>
@@ -10459,32 +10459,32 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O154" t="n">
         <v>1</v>
       </c>
       <c r="P154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -10495,14 +10495,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -10524,26 +10524,26 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O155" t="n">
         <v>1</v>
@@ -10560,7 +10560,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -10589,26 +10589,26 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="O156" t="n">
         <v>1</v>
@@ -10673,7 +10673,7 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -10755,14 +10755,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C159" t="n">
         <v>8</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
         <v>2</v>
@@ -10784,26 +10784,26 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The EV battery example shows the problem that a product passport is desi...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -10820,17 +10820,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C160" t="n">
         <v>9</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -10849,26 +10849,26 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - Evidence ID: CASE_007 Title: 华工正源：马来西亚工厂，公开表述为规避地缘风险 Publisher: C114通信网 ...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N160" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -10895,7 +10895,7 @@
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -10914,22 +10914,22 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The EV battery example shows the problem that a product passport is desi...</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N161" t="n">
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="O162" t="n">
         <v>1</v>
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="O164" t="n">
         <v>1</v>
@@ -11145,14 +11145,14 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C165" t="n">
         <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
         <v>2</v>
@@ -11174,32 +11174,32 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - 35 Appendix Table 1: Leading exporters and importers in world merchandis...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N165" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O165" t="n">
         <v>1</v>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -11210,14 +11210,14 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C166" t="n">
         <v>5</v>
       </c>
       <c r="D166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
         <v>2</v>
@@ -11239,32 +11239,32 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - 35 Appendix Table 1: Leading exporters and importers in world merchandis...</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N166" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="O166" t="n">
         <v>1</v>
       </c>
       <c r="P166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -11323,7 +11323,7 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -11340,14 +11340,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C168" t="n">
         <v>7</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168" t="n">
         <v>2</v>
@@ -11369,26 +11369,26 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N168" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -11405,17 +11405,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C169" t="n">
         <v>8</v>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -11434,26 +11434,26 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N169" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -11470,17 +11470,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C170" t="n">
         <v>9</v>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -11499,26 +11499,26 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N170" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -11629,26 +11629,26 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N172" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="O172" t="n">
         <v>1</v>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -11694,26 +11694,26 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N173" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="O173" t="n">
         <v>1</v>
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O174" t="n">
         <v>1</v>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - The United States under President Trump will simply not allow its manufa...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - 12 V. The Costs to America of China-Linked Transshipment Estimating tota...</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="O175" t="n">
         <v>1</v>
@@ -11860,17 +11860,17 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>5</v>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -11889,32 +11889,32 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O176" t="n">
         <v>1</v>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -11925,17 +11925,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C177" t="n">
         <v>6</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -11954,32 +11954,32 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
       </c>
       <c r="P177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - Evidence ID: MOFCOM_001 Title: 2026年度《两用物项和技术进出口许可证管理目录》 Publisher: 商务部、...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -12055,7 +12055,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -12084,26 +12084,26 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - 3%), while those of the CIS region would contract (-2. 0%). On the expor...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The European Union, with a supranational authority and a single market b...</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -12130,7 +12130,7 @@
         <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -12149,26 +12149,26 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 天孚通信：光引擎垄断者 天孚通信是全球光引擎市场龙头，占据60%以上份额，产品价值占CPO模块的30%-40%。 2025年预计归母净利润18....</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -12185,14 +12185,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>10</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
         <v>2</v>
@@ -12214,26 +12214,26 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The European Union, with a supranational authority and a single market b...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N181" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -12298,7 +12298,7 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O182" t="n">
         <v>1</v>
@@ -12363,7 +12363,7 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="O183" t="n">
         <v>1</v>
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O184" t="n">
         <v>1</v>
@@ -12493,7 +12493,7 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="O185" t="n">
         <v>1</v>
@@ -12623,7 +12623,7 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -12688,7 +12688,7 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O192" t="n">
         <v>1</v>
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="O193" t="n">
         <v>1</v>
@@ -13030,14 +13030,14 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C194" t="n">
         <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E194" t="n">
         <v>2</v>
@@ -13059,12 +13059,12 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -13078,13 +13078,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="O194" t="n">
         <v>1</v>
       </c>
       <c r="P194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="O195" t="n">
         <v>1</v>
@@ -13160,14 +13160,14 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C196" t="n">
         <v>5</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" t="n">
         <v>2</v>
@@ -13189,12 +13189,12 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N196" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="O196" t="n">
         <v>1</v>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -13290,14 +13290,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C198" t="n">
         <v>7</v>
       </c>
       <c r="D198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E198" t="n">
         <v>2</v>
@@ -13319,32 +13319,32 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Furthermore, Vietnam Sunergy Joint Stock Company, a non-mandatory respon...</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N198" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
       </c>
       <c r="P198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -13355,14 +13355,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C199" t="n">
         <v>8</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E199" t="n">
         <v>2</v>
@@ -13384,17 +13384,17 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -13403,13 +13403,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -13449,17 +13449,17 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -13468,7 +13468,7 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -13485,14 +13485,14 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C201" t="n">
         <v>10</v>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E201" t="n">
         <v>2</v>
@@ -13514,26 +13514,26 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - (1349) Should the exports by one of the companies benefiting from lower ...</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N201" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O202" t="n">
         <v>1</v>
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="O203" t="n">
         <v>1</v>
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="O204" t="n">
         <v>1</v>
@@ -13793,7 +13793,7 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O205" t="n">
         <v>1</v>
@@ -13858,7 +13858,7 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="O206" t="n">
         <v>1</v>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -13904,26 +13904,26 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N207" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -13969,26 +13969,26 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N208" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -14070,14 +14070,14 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>FR_001</t>
         </is>
       </c>
       <c r="C210" t="n">
         <v>9</v>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E210" t="n">
         <v>2</v>
@@ -14099,26 +14099,26 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>Federal Register API（美国联邦公报） - Evidence ID: FR_001 Title: Federal Register API（美国联邦公报） Publisher: 美国国家档...</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国家档案馆联邦公报办公室</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>出口管制/关税</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N210" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ITA_001</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -14164,22 +14164,22 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>美国国际贸易管理局（ITA）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N211" t="n">
@@ -14248,7 +14248,7 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O212" t="n">
         <v>1</v>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O213" t="n">
         <v>1</v>
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O214" t="n">
         <v>1</v>
@@ -14395,14 +14395,14 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C215" t="n">
         <v>4</v>
       </c>
       <c r="D215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E215" t="n">
         <v>2</v>
@@ -14424,17 +14424,17 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - This approach is intentionally broad because it can count all trade in a...</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
@@ -14443,7 +14443,7 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="O215" t="n">
         <v>1</v>
@@ -14460,14 +14460,14 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C216" t="n">
         <v>5</v>
       </c>
       <c r="D216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E216" t="n">
         <v>2</v>
@@ -14489,17 +14489,17 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
@@ -14525,14 +14525,14 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C217" t="n">
         <v>6</v>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E217" t="n">
         <v>2</v>
@@ -14554,17 +14554,17 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -14590,14 +14590,14 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C218" t="n">
         <v>7</v>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
         <v>2</v>
@@ -14619,17 +14619,17 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - -154 - 序号 商品名称 描述 海关商品 编号 单位 125 激 光系 统 （ AVLIS，MLIS 和 CRISLA） 为铀同位素分离专门...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
@@ -14638,7 +14638,7 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -14665,7 +14665,7 @@
         <v>0</v>
       </c>
       <c r="E219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -14684,26 +14684,26 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N219" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -14720,14 +14720,14 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C220" t="n">
         <v>9</v>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E220" t="n">
         <v>2</v>
@@ -14749,17 +14749,17 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - The Historical Predicate In plain terms, illegal transshipment is smuggl...</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
@@ -14768,7 +14768,7 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -14785,14 +14785,14 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C221" t="n">
         <v>10</v>
       </c>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221" t="n">
         <v>2</v>
@@ -14814,17 +14814,17 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -14833,7 +14833,7 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14898,7 +14898,7 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="O222" t="n">
         <v>1</v>
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -14944,12 +14944,12 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14963,7 +14963,7 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O223" t="n">
         <v>1</v>
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="O224" t="n">
         <v>1</v>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -15074,12 +15074,12 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -15093,7 +15093,7 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="O225" t="n">
         <v>1</v>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -15139,12 +15139,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 专业领域 税务 全球贸易 2026年8月13日 转运执法加紧 白宫报告《 大转运骗局 》将非法转运列为主要的关税规避风险，估计年流动额在400亿...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -15158,7 +15158,7 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="O226" t="n">
         <v>1</v>
@@ -15223,7 +15223,7 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -15288,7 +15288,7 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -15305,14 +15305,14 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C229" t="n">
         <v>8</v>
       </c>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E229" t="n">
         <v>2</v>
@@ -15334,26 +15334,26 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N229" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -15418,7 +15418,7 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -15464,26 +15464,26 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N231" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -15548,7 +15548,7 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O232" t="n">
         <v>1</v>
@@ -15613,7 +15613,7 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="O233" t="n">
         <v>1</v>
@@ -15678,7 +15678,7 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O234" t="n">
         <v>1</v>
@@ -15743,7 +15743,7 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O235" t="n">
         <v>1</v>
@@ -15808,7 +15808,7 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O236" t="n">
         <v>1</v>
@@ -15825,17 +15825,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C237" t="n">
         <v>6</v>
       </c>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -15854,32 +15854,32 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - 中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一...</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N237" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -15890,17 +15890,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C238" t="n">
         <v>7</v>
       </c>
       <c r="D238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -15919,32 +15919,32 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - 中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N238" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
       </c>
       <c r="P238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -15955,14 +15955,14 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C239" t="n">
         <v>8</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239" t="n">
         <v>2</v>
@@ -15984,17 +15984,17 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -16003,7 +16003,7 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -16049,26 +16049,26 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N240" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -16085,17 +16085,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C241" t="n">
         <v>10</v>
       </c>
       <c r="D241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -16114,26 +16114,26 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N241" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="O242" t="n">
         <v>1</v>
@@ -16263,7 +16263,7 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="O243" t="n">
         <v>1</v>
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O244" t="n">
         <v>1</v>
@@ -16345,14 +16345,14 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C245" t="n">
         <v>4</v>
       </c>
       <c r="D245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E245" t="n">
         <v>2</v>
@@ -16374,32 +16374,32 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="O245" t="n">
         <v>1</v>
       </c>
       <c r="P245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -16458,7 +16458,7 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="O246" t="n">
         <v>1</v>
@@ -16475,14 +16475,14 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C247" t="n">
         <v>6</v>
       </c>
       <c r="D247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E247" t="n">
         <v>2</v>
@@ -16504,32 +16504,32 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N247" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
       </c>
       <c r="P247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -16540,14 +16540,14 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C248" t="n">
         <v>7</v>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E248" t="n">
         <v>2</v>
@@ -16569,26 +16569,26 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N248" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -16605,7 +16605,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -16653,7 +16653,7 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -16718,7 +16718,7 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -16745,7 +16745,7 @@
         <v>1</v>
       </c>
       <c r="E251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -16764,26 +16764,26 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N251" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -16848,7 +16848,7 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O252" t="n">
         <v>1</v>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -16913,7 +16913,7 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="O253" t="n">
         <v>1</v>
@@ -16930,7 +16930,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O254" t="n">
         <v>1</v>
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O255" t="n">
         <v>1</v>
@@ -17060,17 +17060,17 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C256" t="n">
         <v>5</v>
       </c>
       <c r="D256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -17089,26 +17089,26 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - This differential is the China tariff itself minus the lower duty actual...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N256" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O256" t="n">
         <v>1</v>
@@ -17125,17 +17125,17 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C257" t="n">
         <v>6</v>
       </c>
       <c r="D257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -17154,26 +17154,26 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N257" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -17219,17 +17219,17 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - This differential is the China tariff itself minus the lower duty actual...</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -17238,7 +17238,7 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -17320,14 +17320,14 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C260" t="n">
         <v>9</v>
       </c>
       <c r="D260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E260" t="n">
         <v>2</v>
@@ -17349,26 +17349,26 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N260" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -17433,7 +17433,7 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -17479,12 +17479,12 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -17498,7 +17498,7 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="O262" t="n">
         <v>1</v>
@@ -17515,7 +17515,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -17563,7 +17563,7 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="O263" t="n">
         <v>1</v>
@@ -17758,7 +17758,7 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="O266" t="n">
         <v>1</v>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -17804,26 +17804,26 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N267" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -17869,26 +17869,26 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N268" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -18083,7 +18083,7 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -18148,7 +18148,7 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="O272" t="n">
         <v>1</v>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -18194,17 +18194,17 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -18213,7 +18213,7 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="O273" t="n">
         <v>1</v>
@@ -18230,14 +18230,14 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C274" t="n">
         <v>3</v>
       </c>
       <c r="D274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E274" t="n">
         <v>2</v>
@@ -18259,12 +18259,12 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -18278,13 +18278,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O274" t="n">
         <v>1</v>
       </c>
       <c r="P274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -18324,17 +18324,17 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -18343,7 +18343,7 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O275" t="n">
         <v>1</v>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -18389,17 +18389,17 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O276" t="n">
         <v>1</v>
@@ -18425,14 +18425,14 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C277" t="n">
         <v>6</v>
       </c>
       <c r="D277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E277" t="n">
         <v>2</v>
@@ -18454,17 +18454,17 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -18473,13 +18473,13 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
       </c>
       <c r="P277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -18490,14 +18490,14 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C278" t="n">
         <v>7</v>
       </c>
       <c r="D278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E278" t="n">
         <v>2</v>
@@ -18519,32 +18519,32 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N278" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
       </c>
       <c r="P278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -18555,14 +18555,14 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C279" t="n">
         <v>8</v>
       </c>
       <c r="D279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E279" t="n">
         <v>2</v>
@@ -18584,32 +18584,32 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N279" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
       </c>
       <c r="P279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -18668,7 +18668,7 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="O282" t="n">
         <v>1</v>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -18844,12 +18844,12 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -18859,11 +18859,11 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N283" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="O283" t="n">
         <v>1</v>
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="O284" t="n">
         <v>1</v>
@@ -18945,7 +18945,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -18974,12 +18974,12 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -18989,11 +18989,11 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N285" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="O285" t="n">
         <v>1</v>
@@ -19010,7 +19010,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -19039,26 +19039,26 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Thomas Kyhl (PensionDanmark); Scott Lester (BHP Group Limited); Renato M...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N286" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O286" t="n">
         <v>1</v>
@@ -19075,17 +19075,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C287" t="n">
         <v>6</v>
       </c>
       <c r="D287" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -19104,32 +19104,32 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - McKinsey &amp; Company Specialist advisory support Clearer regulatory guidan...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N287" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
       </c>
       <c r="P287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>KPMG_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -19169,17 +19169,17 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>KPMG 2026 US Supply Chain Survey - Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher:...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - McKinsey &amp; Company Specialist advisory support Clearer regulatory guidan...</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>毕马威（KPMG）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -19188,7 +19188,7 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -19205,17 +19205,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C289" t="n">
         <v>8</v>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -19234,26 +19234,26 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Thomas Kyhl (PensionDanmark); Scott Lester (BHP Group Limited); Renato M...</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N289" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -19270,14 +19270,14 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>KPMG_001</t>
         </is>
       </c>
       <c r="C290" t="n">
         <v>9</v>
       </c>
       <c r="D290" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E290" t="n">
         <v>2</v>
@@ -19299,32 +19299,32 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - lithium-ion, including separators, whether or not rectangular (including...</t>
+          <t>KPMG 2026 US Supply Chain Survey - Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher:...</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>毕马威（KPMG）</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N290" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
       </c>
       <c r="P290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -19345,7 +19345,7 @@
         <v>0</v>
       </c>
       <c r="E291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -19364,26 +19364,26 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - 中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一...</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N291" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -19513,7 +19513,7 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O293" t="n">
         <v>1</v>
@@ -19578,7 +19578,7 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O294" t="n">
         <v>1</v>
@@ -19643,7 +19643,7 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O295" t="n">
         <v>1</v>
@@ -19660,14 +19660,14 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C296" t="n">
         <v>5</v>
       </c>
       <c r="D296" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E296" t="n">
         <v>2</v>
@@ -19689,32 +19689,32 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N296" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O296" t="n">
         <v>1</v>
       </c>
       <c r="P296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -19725,14 +19725,14 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C297" t="n">
         <v>6</v>
       </c>
       <c r="D297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E297" t="n">
         <v>2</v>
@@ -19754,26 +19754,26 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N297" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -19790,14 +19790,14 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C298" t="n">
         <v>7</v>
       </c>
       <c r="D298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E298" t="n">
         <v>2</v>
@@ -19819,32 +19819,32 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N298" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
       </c>
       <c r="P298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -19855,7 +19855,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -19884,7 +19884,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -19920,7 +19920,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -20033,7 +20033,7 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -20212,7 +20212,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; CASE_002; TRD_003; WH_002</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; CASE_008; CASE_007; TRD_001; EU_003; CASE_002; TRD_003</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -20239,10 +20239,10 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -20251,11 +20251,11 @@
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CASE_001; WH_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -20293,7 +20293,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; WH_002; CASE_003; CASE_002; TRD_003; TRD_001; TRD_002; CASE_001; CASE_008</t>
+          <t>CASE_007; CASE_010; CASE_003; WH_002; CASE_002; TRD_003; TRD_001; TRD_002; CASE_001; CASE_008</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -20370,12 +20370,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001; WH_002; CASE_002; CSIS_001</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; KPMG_001; WH_002; EU_003; UST_001</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -20385,7 +20385,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -20397,10 +20397,10 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -20409,11 +20409,11 @@
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>WH_002; CSIS_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; WH_002; CASE_002; TRD_003</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; CASE_002; WH_002; EU_003</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; WH_002; CASE_002; TRD_003</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; CASE_010; CASE_002; WH_002; EU_003</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; WH_002; WTO_001; CASE_001; CASE_010; CASE_008; CASE_007; TRD_001</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_001; CASE_010; WH_002; CASE_008; CASE_007; CSIS_001; KPMG_001</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20531,7 +20531,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -20565,11 +20565,11 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>WH_002; WTO_001; CASE_001; CASE_010; TRD_001</t>
+          <t>CASE_001; CASE_010; WH_002; CSIS_001; KPMG_001</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; MOFCOM_001; CASE_009; MOFCOM_002; FR_001; ITA_001; WH_002; CSIS_001; CASE_002</t>
+          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; FR_001; ITA_001; IRS_001; EU_003; UST_001</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -20684,7 +20684,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CASE_009; BIS_001; BIS_002; ITA_001; FR_001; WH_002; CASE_002; CSIS_001; CASE_003; WH_001</t>
+          <t>CASE_009; BIS_002; BIS_001; ITA_001; FR_001; WH_002; CSIS_001; CASE_002; IRS_001; UST_001</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CSIS_001; WH_001</t>
+          <t>CSIS_001; UST_001</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -20765,7 +20765,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; ITA_001; MOFCOM_002; FR_001; CSIS_001; WH_002; MOFCOM_001; WH_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; MOFCOM_002; ITA_001; CSIS_001; CASE_010; UST_001; EU_003</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20774,7 +20774,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CSIS_001; MOFCOM_001; WH_001</t>
+          <t>CSIS_001; UST_001; EU_003</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; WH_001; CASE_002; CSIS_001; CASE_003; TRD_003; TRD_001; TRD_002; CASE_009</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; TRD_001; TRD_003; TRD_002; UST_001</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20889,7 +20889,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>WH_001; CSIS_001</t>
+          <t>CSIS_001; UST_001</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; TRD_003; WH_001; TRD_001; ITA_001; CSIS_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; WH_002; ITA_001; CSIS_001; TRD_003; TRD_001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20936,7 +20936,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -20954,10 +20954,10 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -20966,11 +20966,11 @@
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>WH_001; CSIS_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -21008,7 +21008,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; WEF_001; CASE_001; WH_002; MCK_001; TRD_003; WTO_001; TRD_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; MCK_001; EU_004; WEF_001; IRS_001; WH_002; EU_003</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21051,7 +21051,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WEF_001; CASE_001; WH_002; MCK_001; WTO_001</t>
+          <t>IMF_001; UNCTAD_001; CASE_001; MCK_001; EU_004; WEF_001; WH_002</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -21089,7 +21089,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; MOFCOM_001; CASE_004; ITA_001; CASE_001</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; ITA_001</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21122,7 +21122,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; MOFCOM_001; CASE_004; ITA_001; CASE_001</t>
+          <t>WEF_001; UNCTAD_001; CNGOV_001; TRD_003; CASE_007; CASE_008; EU_003; CASE_004; CASE_001; ITA_001</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>UNCTAD_001; IMF_001; WTO_001; WEF_001; MCK_001; TRD_003; CNGOV_001; KPMG_001; CASE_004; CASE_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; CNGOV_001; EU_004; TRD_003; UST_001; CASE_001</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -21231,7 +21231,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_001; MOFCOM_002; WH_002; CASE_003; TRD_001</t>
+          <t>ITA_001; CASE_009; BIS_002; BIS_001; FR_001; MOFCOM_002; MOFCOM_001; CASE_003; IRS_001; WH_002</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -21312,7 +21312,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; WH_002; CASE_002; CSIS_001; CASE_003; MOFCOM_002</t>
+          <t>FR_001; ITA_001; CASE_009; BIS_002; BIS_001; WH_002; UST_001; CASE_002; CSIS_001; MOFCOM_002</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; WH_002; CASE_003; TRD_002; CASE_002; CASE_010; CSIS_001; CASE_007; CASE_001</t>
+          <t>TRD_001; CASE_003; TRD_003; TRD_002; WH_002; CASE_002; CASE_010; IRS_001; UST_001; CSIS_001</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -21417,30 +21417,26 @@
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O17" t="n">
         <v>0.9</v>
       </c>
-      <c r="O17" t="n">
-        <v>0.867</v>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>China; EV Battery; Malaysia; Thailand; United States; Vietnam</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>EV Battery</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>UST_001; CSIS_001</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -21478,7 +21474,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; WH_001; TRD_001; CASE_002; CASE_008; CASE_007</t>
+          <t>TRD_003; CASE_010; WH_002; CSIS_001; WTO_001; WH_001; CASE_002; CASE_008; UST_001; CASE_007</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -21521,7 +21517,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>WTO_001; CSIS_001; WH_001</t>
+          <t>CSIS_001; WTO_001; UST_001</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -21559,7 +21555,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; CASE_008; WH_002; TRD_001; CASE_001; MOFCOM_001; WTO_001; TRD_002; CSIS_001</t>
+          <t>CASE_002; TRD_003; CASE_008; WH_002; CASE_001; TRD_001; EU_003; CSIS_001; CASE_007; IRS_001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -21568,7 +21564,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -21586,10 +21582,10 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O19" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -21598,15 +21594,15 @@
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>WH_002; CASE_001; WTO_001; TRD_002; CSIS_001</t>
+          <t>WH_002; CASE_001; CSIS_001</t>
         </is>
       </c>
       <c r="T19" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -21711,7 +21707,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; CASE_010; WTO_001; WH_001; TRD_001; CSIS_001; CASE_002; CASE_003; TRD_002</t>
+          <t>TRD_003; WH_002; WH_001; WTO_001; CSIS_001; TRD_001; CASE_002; CASE_010; UST_001; EU_003</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -21738,10 +21734,10 @@
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -21750,11 +21746,11 @@
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>WTO_001; WH_001; CSIS_001; CASE_002</t>
+          <t>WTO_001; CSIS_001; CASE_002; UST_001; EU_003</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -21792,7 +21788,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; TRD_003; CASE_003; TRD_001; TRD_002; ITA_001</t>
+          <t>CASE_010; CSIS_001; WH_002; WH_001; CASE_002; CASE_003; TRD_003; TRD_001; FR_001; TRD_002</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -21819,10 +21815,10 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -21831,11 +21827,11 @@
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>CSIS_001; WH_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -21873,7 +21869,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BIS_001; BIS_002; CASE_009; WH_002; CASE_010; CASE_003; MOFCOM_001; CASE_001; CASE_002; MOFCOM_002</t>
+          <t>BIS_001; BIS_002; CASE_009; EU_001; IRS_001; CASE_010; UST_001; CASE_003; WH_002; EU_003</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -21885,7 +21881,7 @@
         <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0.75</v>
@@ -21916,7 +21912,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -21954,7 +21950,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; CSIS_001; WH_001; TRD_001; TRD_002; CASE_009</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; CSIS_001; WH_001; EU_001; TRD_002; TRD_001</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -21997,7 +21993,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>CSIS_001; WH_001</t>
+          <t>CSIS_001; EU_001</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -22035,7 +22031,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; TRD_003; CASE_008; CASE_003; TRD_001; CASE_009</t>
+          <t>CASE_010; WH_002; WH_001; CSIS_001; CASE_002; CASE_008; CASE_003; EU_001; CASE_009; CASE_001</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -22078,7 +22074,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>WH_001; CSIS_001; CASE_008</t>
+          <t>CSIS_001; CASE_008; EU_001</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -22116,7 +22112,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; CNGOV_001; MCK_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -22125,10 +22121,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -22149,7 +22145,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WEF_001; MCK_001; CNGOV_001; TRD_001; TRD_003; TRD_002; CASE_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; CNGOV_001; MCK_001; WEF_001; EU_004; TRD_001; TRD_002; TRD_003</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -22187,7 +22183,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; FR_001; WH_002; CASE_001; MOFCOM_002; CASE_003; WTO_001; CSIS_001</t>
+          <t>BIS_002; CASE_009; BIS_001; FR_001; CASE_001; MOFCOM_002; WH_002; CASE_003; CASE_010; CSIS_001</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -22199,7 +22195,7 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0.8</v>
@@ -22234,7 +22230,7 @@
         </is>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -22268,7 +22264,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010; WH_002; TRD_003; WH_001; CSIS_001; CASE_008; TRD_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002; WH_001; TRD_003; CSIS_001; CASE_008; TRD_001</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -22295,10 +22291,10 @@
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O28" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -22307,11 +22303,11 @@
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>WH_001; CSIS_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -22349,7 +22345,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; DOC_001; CASE_002; CASE_003; CASE_010; WTO_001; CSIS_001; WH_001; CASE_008</t>
+          <t>TRD_003; CASE_002; CASE_003; CASE_010; WH_002; DOC_001; CSIS_001; WTO_001; WH_001; CASE_008</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -22358,28 +22354,28 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O29" t="n">
         <v>0.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.75</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -22388,11 +22384,11 @@
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_003; WTO_001; CSIS_001; WH_001</t>
+          <t>CASE_003; DOC_001; CSIS_001; WTO_001</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -22430,7 +22426,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; WEF_001; MCK_001; KPMG_001; CASE_001; TRD_001; TRD_003</t>
+          <t>IMF_001; CNGOV_001; WTO_001; UNCTAD_001; EU_004; CASE_001; MCK_001; WEF_001; KPMG_001; CASE_008</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -22463,7 +22459,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; CNGOV_001; WEF_001; MCK_001; KPMG_001; CASE_001; TRD_001; TRD_003</t>
+          <t>IMF_001; CNGOV_001; WTO_001; UNCTAD_001; EU_004; CASE_001; MCK_001; WEF_001; KPMG_001; CASE_008</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -22501,7 +22497,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_003; TRD_001; CSIS_001; CASE_002; TRD_003; TRD_002; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_003; CSIS_001; CASE_002; TRD_001; TRD_002; TRD_003; CASE_007</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -22510,7 +22506,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
         <v>0.8</v>
@@ -22528,10 +22524,10 @@
         <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O31" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -22540,11 +22536,11 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>WH_001; CSIS_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -22629,7 +22625,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -22644,7 +22640,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.931</v>
+        <v>0.92</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -22659,7 +22655,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.874</v>
+        <v>0.892</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -22674,7 +22670,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -22689,7 +22685,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.754</v>
+        <v>0.783</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -22749,7 +22745,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1.847</v>
+        <v>1.827</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -22790,7 +22786,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>0.933 / 0.887 / 5</t>
+          <t>0.867 / 0.912 / 5</t>
         </is>
       </c>
     </row>
@@ -22801,11 +22797,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>0.917 / 0.9 / 5</t>
+          <t>0.917 / 0.912 / 5</t>
         </is>
       </c>
     </row>
@@ -22820,7 +22816,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>0.95 / 0.881 / 10</t>
+          <t>0.95 / 0.887 / 10</t>
         </is>
       </c>
     </row>
@@ -22835,7 +22831,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>0.874 / 0.875 / 5</t>
+          <t>0.874 / 0.912 / 5</t>
         </is>
       </c>
     </row>
@@ -22850,7 +22846,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>0.96 / 0.817 / 5</t>
+          <t>0.96 / 0.838 / 5</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/optimized/retrieval_results.xlsx
+++ b/data/evaluation/optimized/retrieval_results.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P401"/>
+  <dimension ref="A1:P431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3930,14 +3930,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3978,13 +3978,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
@@ -4024,12 +4024,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4043,13 +4043,13 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -10413,7 +10413,7 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O153" t="n">
         <v>1</v>
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O154" t="n">
         <v>1</v>
@@ -10543,7 +10543,7 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O155" t="n">
         <v>1</v>
@@ -10608,7 +10608,7 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O156" t="n">
         <v>1</v>
@@ -10673,7 +10673,7 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -20570,14 +20570,14 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C310" t="n">
         <v>9</v>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E310" t="n">
         <v>2</v>
@@ -20599,26 +20599,26 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N310" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O310" t="n">
         <v>0</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>LI_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -20664,17 +20664,17 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>Li Auto Inc. Form 20-F（fiscal year ended December 31, 2025）理想汽车2025财年年报 - Evidence ID: LI_001 Title: Li Auto Inc. Form 20-F（fiscal year ended Dece...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>理想汽车（Li Auto Inc.，SEC EDGAR）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -20683,7 +20683,7 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O311" t="n">
         <v>0</v>
@@ -24860,14 +24860,14 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C376" t="n">
         <v>5</v>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E376" t="n">
         <v>2</v>
@@ -24889,17 +24889,17 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O376" t="n">
         <v>1</v>
@@ -24925,14 +24925,14 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>EU_002</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="C377" t="n">
         <v>6</v>
       </c>
       <c r="D377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E377" t="n">
         <v>2</v>
@@ -24954,17 +24954,17 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -24990,7 +24990,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>EU_002</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -25019,17 +25019,17 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
         </is>
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O378" t="n">
         <v>0</v>
@@ -25055,7 +25055,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -25084,17 +25084,17 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -25103,7 +25103,7 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O379" t="n">
         <v>0</v>
@@ -25120,7 +25120,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -25149,17 +25149,17 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -25185,7 +25185,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -25214,17 +25214,17 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -25233,7 +25233,7 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O381" t="n">
         <v>0</v>
@@ -25380,14 +25380,14 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C384" t="n">
         <v>3</v>
       </c>
       <c r="D384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E384" t="n">
         <v>2</v>
@@ -25409,26 +25409,26 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N384" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="O384" t="n">
         <v>1</v>
@@ -25445,14 +25445,14 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>ALB_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C385" t="n">
         <v>4</v>
       </c>
       <c r="D385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E385" t="n">
         <v>2</v>
@@ -25474,17 +25474,17 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 - Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
@@ -25510,14 +25510,14 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>IEA_001</t>
+          <t>ALB_001</t>
         </is>
       </c>
       <c r="C386" t="n">
         <v>5</v>
       </c>
       <c r="D386" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E386" t="n">
         <v>2</v>
@@ -25539,12 +25539,12 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 - Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ...</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>国际能源署（IEA）</t>
+          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -25554,7 +25554,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N386" t="n">
@@ -25564,7 +25564,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -25575,14 +25575,14 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>IEA_001</t>
         </is>
       </c>
       <c r="C387" t="n">
         <v>6</v>
       </c>
       <c r="D387" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E387" t="n">
         <v>2</v>
@@ -25604,22 +25604,22 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Ph...</t>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>国际能源署（IEA）</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N387" t="n">
@@ -25629,7 +25629,7 @@
         <v>0</v>
       </c>
       <c r="P387" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388">
@@ -25640,14 +25640,14 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C388" t="n">
         <v>7</v>
       </c>
       <c r="D388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E388" t="n">
         <v>2</v>
@@ -25669,26 +25669,26 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA Ph...</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N388" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O388" t="n">
         <v>0</v>
@@ -25705,7 +25705,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -25734,17 +25734,17 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -25770,14 +25770,14 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C390" t="n">
         <v>9</v>
       </c>
       <c r="D390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E390" t="n">
         <v>2</v>
@@ -25799,17 +25799,17 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -25818,7 +25818,7 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O390" t="n">
         <v>0</v>
@@ -25835,7 +25835,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -25864,17 +25864,17 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Jordan offers preferential trade access and niche assembly capacity. Tab...</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
@@ -26539,6 +26539,1956 @@
         <v>0</v>
       </c>
       <c r="P401" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>1</v>
+      </c>
+      <c r="D402" t="n">
+        <v>2</v>
+      </c>
+      <c r="E402" t="n">
+        <v>2</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N402" t="n">
+        <v>63</v>
+      </c>
+      <c r="O402" t="n">
+        <v>1</v>
+      </c>
+      <c r="P402" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>2</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0</v>
+      </c>
+      <c r="E403" t="n">
+        <v>2</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N403" t="n">
+        <v>39</v>
+      </c>
+      <c r="O403" t="n">
+        <v>1</v>
+      </c>
+      <c r="P403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>3</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>2</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N404" t="n">
+        <v>37</v>
+      </c>
+      <c r="O404" t="n">
+        <v>1</v>
+      </c>
+      <c r="P404" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>4</v>
+      </c>
+      <c r="D405" t="n">
+        <v>0</v>
+      </c>
+      <c r="E405" t="n">
+        <v>1</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N405" t="n">
+        <v>33</v>
+      </c>
+      <c r="O405" t="n">
+        <v>1</v>
+      </c>
+      <c r="P405" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>IEA_001</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>5</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0</v>
+      </c>
+      <c r="E406" t="n">
+        <v>2</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>国际能源署（IEA）</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N406" t="n">
+        <v>31</v>
+      </c>
+      <c r="O406" t="n">
+        <v>1</v>
+      </c>
+      <c r="P406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>CSIS_001</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>6</v>
+      </c>
+      <c r="D407" t="n">
+        <v>1</v>
+      </c>
+      <c r="E407" t="n">
+        <v>2</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The EV battery example shows the problem that a product passport is desi...</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>战略与国际研究中心（CSIS）</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N407" t="n">
+        <v>32</v>
+      </c>
+      <c r="O407" t="n">
+        <v>0</v>
+      </c>
+      <c r="P407" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>7</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" t="n">
+        <v>2</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N408" t="n">
+        <v>31</v>
+      </c>
+      <c r="O408" t="n">
+        <v>0</v>
+      </c>
+      <c r="P408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>IRS_001</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>8</v>
+      </c>
+      <c r="D409" t="n">
+        <v>1</v>
+      </c>
+      <c r="E409" t="n">
+        <v>2</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N409" t="n">
+        <v>30</v>
+      </c>
+      <c r="O409" t="n">
+        <v>0</v>
+      </c>
+      <c r="P409" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>9</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" t="n">
+        <v>2</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N410" t="n">
+        <v>29</v>
+      </c>
+      <c r="O410" t="n">
+        <v>0</v>
+      </c>
+      <c r="P410" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>WH_002</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>10</v>
+      </c>
+      <c r="D411" t="n">
+        <v>1</v>
+      </c>
+      <c r="E411" t="n">
+        <v>2</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - 10 logistics platforms may serve both legitimate trade and China-linked ...</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N411" t="n">
+        <v>29</v>
+      </c>
+      <c r="O411" t="n">
+        <v>0</v>
+      </c>
+      <c r="P411" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>1</v>
+      </c>
+      <c r="D412" t="n">
+        <v>2</v>
+      </c>
+      <c r="E412" t="n">
+        <v>2</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N412" t="n">
+        <v>63</v>
+      </c>
+      <c r="O412" t="n">
+        <v>1</v>
+      </c>
+      <c r="P412" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>CASE_002</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>2</v>
+      </c>
+      <c r="D413" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" t="n">
+        <v>2</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>反规避</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N413" t="n">
+        <v>34</v>
+      </c>
+      <c r="O413" t="n">
+        <v>1</v>
+      </c>
+      <c r="P413" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>3</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" t="n">
+        <v>2</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N414" t="n">
+        <v>31</v>
+      </c>
+      <c r="O414" t="n">
+        <v>1</v>
+      </c>
+      <c r="P414" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>UST_001</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>4</v>
+      </c>
+      <c r="D415" t="n">
+        <v>1</v>
+      </c>
+      <c r="E415" t="n">
+        <v>2</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N415" t="n">
+        <v>30</v>
+      </c>
+      <c r="O415" t="n">
+        <v>1</v>
+      </c>
+      <c r="P415" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>TRD_001</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>5</v>
+      </c>
+      <c r="D416" t="n">
+        <v>1</v>
+      </c>
+      <c r="E416" t="n">
+        <v>2</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>贸易流</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N416" t="n">
+        <v>30</v>
+      </c>
+      <c r="O416" t="n">
+        <v>1</v>
+      </c>
+      <c r="P416" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>6</v>
+      </c>
+      <c r="D417" t="n">
+        <v>0</v>
+      </c>
+      <c r="E417" t="n">
+        <v>1</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N417" t="n">
+        <v>30</v>
+      </c>
+      <c r="O417" t="n">
+        <v>0</v>
+      </c>
+      <c r="P417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>IEA_001</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>7</v>
+      </c>
+      <c r="D418" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" t="n">
+        <v>2</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>国际能源署（IEA）</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N418" t="n">
+        <v>29</v>
+      </c>
+      <c r="O418" t="n">
+        <v>0</v>
+      </c>
+      <c r="P418" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>8</v>
+      </c>
+      <c r="D419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" t="n">
+        <v>2</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 - Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ...</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N419" t="n">
+        <v>28</v>
+      </c>
+      <c r="O419" t="n">
+        <v>0</v>
+      </c>
+      <c r="P419" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>WH_002</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>9</v>
+      </c>
+      <c r="D420" t="n">
+        <v>1</v>
+      </c>
+      <c r="E420" t="n">
+        <v>2</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - As illustrated by these pairings, when China-origin goods enter the U. S...</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N420" t="n">
+        <v>27</v>
+      </c>
+      <c r="O420" t="n">
+        <v>0</v>
+      </c>
+      <c r="P420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>10</v>
+      </c>
+      <c r="D421" t="n">
+        <v>0</v>
+      </c>
+      <c r="E421" t="n">
+        <v>2</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N421" t="n">
+        <v>27</v>
+      </c>
+      <c r="O421" t="n">
+        <v>0</v>
+      </c>
+      <c r="P421" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>EU_002</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>1</v>
+      </c>
+      <c r="D422" t="n">
+        <v>2</v>
+      </c>
+      <c r="E422" t="n">
+        <v>2</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2024/1252 establishing a framework for ensuring a secure and sustainable supply of critical raw materials（欧盟关键原材料法案 CRMA） - Evidence ID: EU_002 Title: Regulation (EU) 2024/1252 establishing a fram...</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>本地化政策</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N422" t="n">
+        <v>53</v>
+      </c>
+      <c r="O422" t="n">
+        <v>1</v>
+      </c>
+      <c r="P422" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>2</v>
+      </c>
+      <c r="D423" t="n">
+        <v>2</v>
+      </c>
+      <c r="E423" t="n">
+        <v>2</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N423" t="n">
+        <v>52</v>
+      </c>
+      <c r="O423" t="n">
+        <v>1</v>
+      </c>
+      <c r="P423" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>3</v>
+      </c>
+      <c r="D424" t="n">
+        <v>0</v>
+      </c>
+      <c r="E424" t="n">
+        <v>2</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>劳工</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N424" t="n">
+        <v>41</v>
+      </c>
+      <c r="O424" t="n">
+        <v>1</v>
+      </c>
+      <c r="P424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>4</v>
+      </c>
+      <c r="D425" t="n">
+        <v>0</v>
+      </c>
+      <c r="E425" t="n">
+        <v>2</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>市场准入</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N425" t="n">
+        <v>38</v>
+      </c>
+      <c r="O425" t="n">
+        <v>1</v>
+      </c>
+      <c r="P425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>5</v>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="n">
+        <v>2</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>关税</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N426" t="n">
+        <v>34</v>
+      </c>
+      <c r="O426" t="n">
+        <v>1</v>
+      </c>
+      <c r="P426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>WH_002</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>6</v>
+      </c>
+      <c r="D427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E427" t="n">
+        <v>2</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - They are product-to-industry matches: foreign corridors handling high-ri...</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>原产地与转运</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N427" t="n">
+        <v>34</v>
+      </c>
+      <c r="O427" t="n">
+        <v>0</v>
+      </c>
+      <c r="P427" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>SNE_001</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>7</v>
+      </c>
+      <c r="D428" t="n">
+        <v>0</v>
+      </c>
+      <c r="E428" t="n">
+        <v>1</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>SNE Research</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N428" t="n">
+        <v>33</v>
+      </c>
+      <c r="O428" t="n">
+        <v>0</v>
+      </c>
+      <c r="P428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>MOFCOM_002</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>8</v>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" t="n">
+        <v>2</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>商务部</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>出口管制</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N429" t="n">
+        <v>32</v>
+      </c>
+      <c r="O429" t="n">
+        <v>0</v>
+      </c>
+      <c r="P429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>9</v>
+      </c>
+      <c r="D430" t="n">
+        <v>0</v>
+      </c>
+      <c r="E430" t="n">
+        <v>2</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 - Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ...</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="N430" t="n">
+        <v>32</v>
+      </c>
+      <c r="O430" t="n">
+        <v>0</v>
+      </c>
+      <c r="P430" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>IEA_001</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>10</v>
+      </c>
+      <c r="D431" t="n">
+        <v>0</v>
+      </c>
+      <c r="E431" t="n">
+        <v>2</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>国际能源署（IEA）</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>供应链布局</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="N431" t="n">
+        <v>32</v>
+      </c>
+      <c r="O431" t="n">
+        <v>0</v>
+      </c>
+      <c r="P431" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26553,7 +28503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U41"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -27107,7 +29057,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BIS_002; BIS_001; CASE_009; MOFCOM_002; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
+          <t>BIS_002; BIS_001; MOFCOM_002; CASE_009; MOFCOM_001; NIO_001; XPEV_001; DHS_001; EU_003; IRS_001</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -29042,7 +30992,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; DHS_001; WH_002; UST_001; SNE_001; IEA_001; CSIS_001; IRS_001; LI_001</t>
+          <t>TSLA_001; EU_003; DHS_001; WH_002; UST_001; SNE_001; IEA_001; CSIS_001; TRD_001; IRS_001</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -29595,7 +31545,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; EU_002; BIS_001; USMCA_001; CASE_002; UST_001</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; MOFCOM_002; TSLA_001; EU_002; BIS_001; USMCA_001; CASE_002</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -29607,7 +31557,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -29622,10 +31572,10 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -29634,13 +31584,9 @@
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>9</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>UST_001</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="n">
         <v>1.8</v>
       </c>
@@ -29676,7 +31622,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SNE_001; DHS_001; EU_003; ALB_001; IEA_001; CSIS_001; IRS_001; UST_001; TSLA_001; WH_002</t>
+          <t>SNE_001; DHS_001; TRD_001; EU_003; ALB_001; IEA_001; CSIS_001; IRS_001; UST_001; TSLA_001</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -29685,7 +31631,7 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>0.6</v>
@@ -29703,10 +31649,10 @@
         <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O40" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -29715,11 +31661,11 @@
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>CSIS_001; UST_001; WH_002</t>
+          <t>CSIS_001; UST_001</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -29807,6 +31753,249 @@
         <v>2</v>
       </c>
       <c r="U41" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>EU_001; DHS_001; EU_003; SNE_001; IEA_001; CSIS_001; UST_001; IRS_001; TSLA_001; WH_002</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>CSIS_001; UST_001; WH_002</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>EU_003; CASE_002; DHS_001; UST_001; TRD_001; SNE_001; IEA_001; ALB_001; WH_002; EU_001</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>AD/CVD; China; EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="n">
+        <v>8</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>UST_001; WH_002</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004; DHS_001; EU_001; EU_003; WH_002; SNE_001; MOFCOM_002; ALB_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>China; EU; EV Battery</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>9</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>WH_002</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -29855,7 +32044,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
@@ -29885,7 +32074,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.835</v>
+        <v>0.8</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -29900,7 +32089,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.919</v>
+        <v>0.925</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -29915,7 +32104,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -29945,7 +32134,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.839</v>
+        <v>0.842</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -29960,11 +32149,11 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>of 40; entity-free questions excluded</t>
+          <t>of 43; entity-free questions excluded</t>
         </is>
       </c>
     </row>
@@ -30005,7 +32194,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1.87</v>
+        <v>1.874</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -30057,11 +32246,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.886</v>
+        <v>0.8</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>0.94 / 0.958 / 7</t>
+          <t>0.948 / 0.943 / 8</t>
         </is>
       </c>
     </row>
@@ -30072,11 +32261,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.85</v>
+        <v>0.786</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>0.958 / 0.93 / 12</t>
+          <t>0.964 / 0.933 / 14</t>
         </is>
       </c>
     </row>
@@ -30106,7 +32295,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>0.948 / 0.875 / 7</t>
+          <t>0.948 / 0.883 / 7</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/optimized/retrieval_results.xlsx
+++ b/data/evaluation/optimized/retrieval_results.xlsx
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1655,14 +1655,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -1684,17 +1684,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告） - Evidence ID: WB_001 Title: Connecting to Compete 2023: Trade Logistics i...</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>物流</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1720,14 +1720,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -1749,17 +1749,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Connecting to Compete 2023: Trade Logistics in an Uncertain Global Economy（2023年物流绩效指数报告） - Evidence ID: WB_001 Title: Connecting to Compete 2023: Trade Logistics i...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>物流</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CASE_006</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 截至9月30日，阿里云在全球29个地区运营着91个可用区，并宣布在巴西、法国和荷兰新建数据中心。 同时，阿里上线千问App，向AI to C领域...</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CASE_006</t>
+          <t>CASE_005</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向...</t>
+          <t>新易盛：2022年设立泰国基地，一二期已投产 - 玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向...</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CASE_005</t>
+          <t>CASE_006</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>新易盛：2022年设立泰国基地，一二期已投产 - 玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向...</t>
+          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 玻色量子这座工厂的意义，不仅在于“造出一台量子计算机”，更在于建立了一套可复制、可扩展的量子硬件制造标准。 它标志着我国在量子计算从“实验室走向...</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O74" t="n">
         <v>1</v>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -6949,22 +6949,22 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N100" t="n">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -7014,26 +7014,26 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8589,11 +8589,11 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N125" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O125" t="n">
         <v>1</v>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8654,11 +8654,11 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O133" t="n">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O134" t="n">
         <v>1</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O135" t="n">
         <v>1</v>
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="O136" t="n">
         <v>1</v>
@@ -9373,7 +9373,7 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="O143" t="n">
         <v>1</v>
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O144" t="n">
         <v>1</v>
@@ -10365,14 +10365,14 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C153" t="n">
         <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
@@ -10394,22 +10394,22 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N153" t="n">
@@ -10419,7 +10419,7 @@
         <v>1</v>
       </c>
       <c r="P153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -10459,17 +10459,17 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -10478,7 +10478,7 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O154" t="n">
         <v>1</v>
@@ -10495,14 +10495,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C155" t="n">
         <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
         <v>2</v>
@@ -10524,32 +10524,32 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O155" t="n">
         <v>1</v>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TRD_002</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -10589,26 +10589,26 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O156" t="n">
         <v>1</v>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>TRD_002</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -10654,26 +10654,26 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度 - Evidence ID: TRD_002 Title: 美国自越南、泰国、马来西亚、柬埔寨进口光伏组件HS 854140，2018–2025年度...</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O162" t="n">
         <v>1</v>
@@ -11063,7 +11063,7 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O163" t="n">
         <v>1</v>
@@ -11323,7 +11323,7 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -11648,7 +11648,7 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O172" t="n">
         <v>1</v>
@@ -11778,7 +11778,7 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O174" t="n">
         <v>1</v>
@@ -11843,7 +11843,7 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O175" t="n">
         <v>1</v>
@@ -11860,14 +11860,14 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="C176" t="n">
         <v>5</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E176" t="n">
         <v>2</v>
@@ -11889,17 +11889,17 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -11908,7 +11908,7 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O176" t="n">
         <v>1</v>
@@ -11925,14 +11925,14 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C177" t="n">
         <v>6</v>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E177" t="n">
         <v>2</v>
@@ -11954,17 +11954,17 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -11973,7 +11973,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -11990,17 +11990,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C178" t="n">
         <v>7</v>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -12019,32 +12019,32 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -12055,14 +12055,14 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>8</v>
       </c>
       <c r="D179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" t="n">
         <v>1</v>
@@ -12084,12 +12084,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -12099,17 +12099,17 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
       </c>
       <c r="P179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -12120,17 +12120,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C180" t="n">
         <v>9</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -12149,26 +12149,26 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -12185,14 +12185,14 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>10</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
         <v>2</v>
@@ -12214,26 +12214,26 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N181" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -12640,17 +12640,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CASE_004</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C188" t="n">
         <v>7</v>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -12669,32 +12669,32 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N188" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
       </c>
       <c r="P188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -12770,17 +12770,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_004</t>
         </is>
       </c>
       <c r="C190" t="n">
         <v>9</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -12799,32 +12799,32 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>中际旭创：泰国工厂产能与国内基本齐平 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>国盛证券（经腾讯新闻转载）</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N190" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
       </c>
       <c r="P190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O192" t="n">
         <v>1</v>
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O193" t="n">
         <v>1</v>
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O195" t="n">
         <v>1</v>
@@ -13225,14 +13225,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C197" t="n">
         <v>6</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E197" t="n">
         <v>2</v>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - disclosing certain foreign tax and global business identi- fiers; and pr...</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -13355,14 +13355,14 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C199" t="n">
         <v>8</v>
       </c>
       <c r="D199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E199" t="n">
         <v>2</v>
@@ -13384,12 +13384,12 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - disclosing certain foreign tax and global business identi- fiers; and pr...</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -13409,7 +13409,7 @@
         <v>0</v>
       </c>
       <c r="P199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -13663,7 +13663,7 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O203" t="n">
         <v>1</v>
@@ -14005,14 +14005,14 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C209" t="n">
         <v>8</v>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E209" t="n">
         <v>2</v>
@@ -14034,26 +14034,26 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N209" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -14070,14 +14070,14 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C210" t="n">
         <v>9</v>
       </c>
       <c r="D210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E210" t="n">
         <v>2</v>
@@ -14099,22 +14099,22 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O214" t="n">
         <v>1</v>
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O255" t="n">
         <v>1</v>
@@ -17710,7 +17710,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -17739,26 +17739,26 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N266" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O266" t="n">
         <v>1</v>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -17804,26 +17804,26 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N267" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -18148,7 +18148,7 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O272" t="n">
         <v>1</v>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -18324,17 +18324,17 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -18389,17 +18389,17 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 进口商应预期，如果新关税措施后采购模式发生变化，来自高关税国家的货物经由中介管辖区转运，或声称的原产国缺乏有意义生产证据，原产地主张将受到更严格...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O276" t="n">
         <v>1</v>
@@ -19773,7 +19773,7 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -19838,7 +19838,7 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -19855,7 +19855,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -19884,22 +19884,22 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N299" t="n">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -19949,26 +19949,26 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N300" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -20618,7 +20618,7 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O310" t="n">
         <v>0</v>
@@ -20878,7 +20878,7 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O314" t="n">
         <v>1</v>
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O315" t="n">
         <v>1</v>
@@ -21090,7 +21090,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -21119,7 +21119,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -21155,7 +21155,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>MOFCOM_001</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -21184,12 +21184,12 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>2026年度《两用物项和技术进出口许可证管理目录》 - - 17 - Ⅱ、两用物项和技术出口许可证管理目录 一、两用物项出口管制清单所列物项 （一）专用材料和相关设备、化学制品、微生物和毒素 1A 系...</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>美国商务部工业与安全局（BIS）</t>
+          <t>商务部、海关总署</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -21203,7 +21203,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O319" t="n">
         <v>0</v>
@@ -21220,7 +21220,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>MOFCOM_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -21249,12 +21249,12 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>2026年度《两用物项和技术进出口许可证管理目录》 - - 17 - Ⅱ、两用物项和技术出口许可证管理目录 一、两用物项出口管制清单所列物项 （一）专用材料和相关设备、化学制品、微生物和毒素 1A 系...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>商务部、海关总署</t>
+          <t>美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -21610,14 +21610,14 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C326" t="n">
         <v>5</v>
       </c>
       <c r="D326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E326" t="n">
         <v>2</v>
@@ -21639,26 +21639,26 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - _x_tr_sch=http&amp;_x_tr_sl=auto&amp;_x_tr_tl=en&amp;_x_tr_hl=en&amp;_x_tr_pto=wapp Appe...</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N326" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O326" t="n">
         <v>1</v>
@@ -21675,14 +21675,14 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C327" t="n">
         <v>6</v>
       </c>
       <c r="D327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E327" t="n">
         <v>2</v>
@@ -21704,26 +21704,26 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - _x_tr_sch=http&amp;_x_tr_sl=auto&amp;_x_tr_tl=en&amp;_x_tr_hl=en&amp;_x_tr_pto=wapp Appe...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N327" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O327" t="n">
         <v>0</v>
@@ -22520,7 +22520,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -22530,7 +22530,7 @@
         <v>1</v>
       </c>
       <c r="E340" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -22549,22 +22549,22 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Between 28 February and 9 March 2026, the ongoing regional conflict led ...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N340" t="n">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -22595,7 +22595,7 @@
         <v>1</v>
       </c>
       <c r="E341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -22614,22 +22614,22 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Between 28 February and 9 March 2026, the ongoing regional conflict led ...</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N341" t="n">
@@ -23235,7 +23235,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>ITA_001</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -23245,7 +23245,7 @@
         <v>0</v>
       </c>
       <c r="E351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G351" t="inlineStr">
         <is>
@@ -23264,22 +23264,22 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Consolidated Screening List API（美国合并筛查清单） - Evidence ID: ITA_001 Title: Consolidated Screening List API（美国合并筛查清单） Pu...</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国国际贸易管理局（ITA）</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N351" t="n">
@@ -24128,7 +24128,7 @@
         </is>
       </c>
       <c r="N364" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O364" t="n">
         <v>1</v>
@@ -25428,7 +25428,7 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O384" t="n">
         <v>1</v>
@@ -28743,7 +28743,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; IEA_001; WH_002; CASE_003; CASE_002; TRD_003; TRD_001; WB_001; CASE_001</t>
+          <t>CASE_007; CASE_010; IEA_001; WH_002; CASE_003; CASE_002; TRD_003; WB_001; TRD_001; CASE_001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -28824,7 +28824,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_008; CASE_007; CASE_006; CASE_004; CASE_005; IEA_001; SNE_001; TSLA_001; ALB_001</t>
+          <t>CASE_001; CASE_008; CASE_007; CASE_004; CASE_006; CASE_005; IEA_001; SNE_001; TSLA_001; ALB_001</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -28905,7 +28905,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; SNE_001; IEA_001; CASE_010; CASE_002</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_005; CASE_006; SNE_001; IEA_001; CASE_010; CASE_002</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -28938,7 +28938,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_006; CASE_005; SNE_001; IEA_001; CASE_010; CASE_002</t>
+          <t>CASE_008; CASE_007; CASE_001; CASE_004; CASE_005; CASE_006; SNE_001; IEA_001; CASE_010; CASE_002</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -29369,7 +29369,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; USMCA_001; WH_002; DHS_001; TRD_003; CSIS_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; USMCA_001; WH_002; DHS_001; CSIS_001; TRD_003</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -29598,7 +29598,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; WEF_001; MCK_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -29631,7 +29631,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; WEF_001; MCK_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -29827,7 +29827,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_003; DHS_001; TRD_002; WH_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
+          <t>TRD_001; CASE_003; DHS_001; TRD_003; WH_002; TRD_002; CASE_002; CASE_010; IRS_001; SNE_001</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -29985,7 +29985,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; EU_003; TSLA_001; TRD_001; CASE_001; SNE_001; IRS_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; TSLA_001; EU_003; CASE_001; SNE_001; IRS_001; TRD_001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -29997,7 +29997,7 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0.8</v>
@@ -30066,7 +30066,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_004; CASE_007; CASE_003; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_003; CASE_007; CASE_004; CASE_006</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -30099,7 +30099,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_004; CASE_007; CASE_003; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_003; CASE_007; CASE_004; CASE_006</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -30137,7 +30137,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; WTO_001; TRD_001; CSIS_001; USMCA_001; WH_001; CASE_010; DHS_001; IEA_001</t>
+          <t>TRD_003; WH_002; WTO_001; TRD_001; CSIS_001; CASE_010; USMCA_001; WH_001; DHS_001; IEA_001</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -30218,7 +30218,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; TRD_003; DHS_001; TRD_001</t>
+          <t>CASE_010; CSIS_001; WH_002; USMCA_001; WH_001; CASE_002; CASE_003; DHS_001; TRD_003; TRD_001</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; TRD_003; WH_001; CSIS_001; USMCA_001; CASE_008; CASE_010</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; WH_001; TRD_003; CSIS_001; USMCA_001; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -30763,7 +30763,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_003; CASE_010; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -30915,7 +30915,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; TRD_001; TRD_002; TRD_003; USMCA_001; CASE_007</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; TRD_001; TRD_002; USMCA_001; TRD_003; CASE_007</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -31073,7 +31073,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NIO_001; XPEV_001; FR_001; ITA_001; BIS_002; MOFCOM_002; CASE_009; BIS_001; MOFCOM_001; TSLA_001</t>
+          <t>NIO_001; XPEV_001; FR_001; ITA_001; BIS_002; MOFCOM_002; BIS_001; MOFCOM_001; CASE_009; TSLA_001</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -31154,7 +31154,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; WH_002; SNE_001; TRD_001; EU_003; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
+          <t>ALB_001; DHS_001; WH_002; SNE_001; EU_003; TRD_001; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -31166,7 +31166,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -31187,7 +31187,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; WH_002; SNE_001; TRD_001; EU_003; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
+          <t>ALB_001; DHS_001; WH_002; SNE_001; EU_003; TRD_001; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -31225,7 +31225,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>USMCA_001; WH_002; CASE_002; DHS_001; CSIS_001; UST_001; EU_003; IRS_001; WTO_001; SNE_001</t>
+          <t>USMCA_001; WH_002; CASE_002; DHS_001; CSIS_001; UST_001; EU_003; IRS_001; SNE_001; WTO_001</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -31306,7 +31306,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; WH_002; DHS_001; IRS_001; UST_001; WTO_004; SNE_001; IEA_001; CASE_001</t>
+          <t>WTO_002; WTO_003; WH_002; DHS_001; IRS_001; UST_001; WTO_004; SNE_001; IEA_001; ITA_001</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -31333,10 +31333,10 @@
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O36" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -31345,11 +31345,11 @@
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>WH_002; DHS_001; IRS_001; WTO_004; SNE_001</t>
+          <t>WH_002; DHS_001; IRS_001; WTO_004; SNE_001; ITA_001</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -32104,7 +32104,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.842</v>
+        <v>0.839</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.85</v>
+        <v>0.825</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>0.964 / 0.933 / 14</t>
+          <t>0.964 / 0.929 / 14</t>
         </is>
       </c>
     </row>
@@ -32291,7 +32291,7 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>0.743</v>
+        <v>0.771</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>

--- a/data/evaluation/optimized/retrieval_results.xlsx
+++ b/data/evaluation/optimized/retrieval_results.xlsx
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1070,14 +1070,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -1099,26 +1099,26 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1135,14 +1135,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -1164,26 +1164,26 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1785,17 +1785,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WTO_004</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>10</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1814,22 +1814,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - Layout Designs of Integrated Circuits Law Maximum IDR 300 million fine. ...</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -3420,7 +3420,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3439,22 +3439,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Introduction Every year, the United States loses tens of billions of dol...</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - China began levying a 2% consumption tax on lithium-ion batteries sold d...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3550,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -3569,26 +3569,26 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Introduction Every year, the United States loses tens of billions of dol...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - China began levying a 2% consumption tax on lithium-ion batteries sold d...</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IEA_001</t>
+          <t>ALB_001</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Across all vehicle modes, excluding 2/3Ws, EVs represent 1 in 8 vehicles...</t>
+          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 - Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ...</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>国际能源署（IEA）</t>
+          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>IEA_001</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3745,7 +3745,7 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Across all vehicle modes, excluding 2/3Ws, EVs represent 1 in 8 vehicles...</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>国际能源署（IEA）</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3779,11 +3779,11 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
@@ -4043,7 +4043,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O66" t="n">
         <v>1</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O72" t="n">
         <v>1</v>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="O83" t="n">
         <v>1</v>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -6104,17 +6104,17 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -6169,17 +6169,17 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Evidence ID: CASE_003 Title: 同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet...</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O92" t="n">
         <v>1</v>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>WH_001</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>美国白宫</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6708,7 +6708,7 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O96" t="n">
         <v>1</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>WH_001</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+          <t>Executive Order 14411: Strengthening Customs Enforcement（加强海关执法行政令） - Evidence ID: WH_001 Title: Executive Order 14411: Strengthening Customs ...</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>美国白宫</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6838,7 +6838,7 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -6920,7 +6920,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -6949,26 +6949,26 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
+          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -6985,7 +6985,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -7014,26 +7014,26 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - Evidence ID: CSIS_001 Title: The Visibility Gap: How AI Can Stop Chinese...</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -7050,14 +7050,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
         <v>2</v>
@@ -7079,12 +7079,12 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现...</t>
+          <t>对外投资合作国别（地区）指南：印度（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7098,13 +7098,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
       <c r="P102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -7115,14 +7115,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E103" t="n">
         <v>2</v>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>国际货币基金组织（IMF）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7159,17 +7159,17 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
       </c>
       <c r="P103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 中华⼈⺠共和国国务院令中华⼈⺠共和国国务院令 第 837 号 《国务院关于对外投资的规定》已经2026年4⽉17⽇国务院第83次常务会议通过，现...</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7224,11 +7224,11 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N104" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="O104" t="n">
         <v>1</v>
@@ -7245,17 +7245,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -7274,26 +7274,26 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>对外投资合作国别（地区）指南：泰国（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N105" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="O105" t="n">
         <v>1</v>
@@ -7310,14 +7310,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>5</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
         <v>2</v>
@@ -7339,17 +7339,17 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="O106" t="n">
         <v>1</v>
@@ -7375,17 +7375,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>6</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -7404,32 +7404,32 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+          <t>World Economic Outlook, April 2023, Chapter 4: Geoeconomic Fragmentation and Foreign Direct Investment - Evidence ID: IMF_001 Title: World Economic Outlook, April 2023, Chapter ...</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>国际货币基金组织（IMF）</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -7440,14 +7440,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>7</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
         <v>2</v>
@@ -7469,32 +7469,32 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Once leaders have defined their objectives, they can choose from a tool ...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N108" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -7534,26 +7534,26 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N109" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -7570,14 +7570,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>9</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
         <v>2</v>
@@ -7599,26 +7599,26 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Lashley, Senior Fellow Don Marshall, Professor Kenisha Chase, Research A...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N110" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -7635,7 +7635,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -7645,7 +7645,7 @@
         <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -7664,26 +7664,26 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N111" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O112" t="n">
         <v>1</v>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O113" t="n">
         <v>1</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" t="n">
         <v>2</v>
@@ -7859,12 +7859,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - China remained the fourth largest destination for FDI in 2025, with tren...</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版） - 4. 投资环境 4.1 投资吸引力 【主要优势】越南吸引外资的主要优势：一是政局稳定，经济发展较快。越南政 府执政能力较强，政策具有连续性，注重...</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7874,17 +7874,17 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O114" t="n">
         <v>1</v>
       </c>
       <c r="P114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -7895,14 +7895,14 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>4</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" t="n">
         <v>2</v>
@@ -7924,12 +7924,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - China remained the fourth largest destination for FDI in 2025, with tren...</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7939,17 +7939,17 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O115" t="n">
         <v>1</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -7960,14 +7960,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>5</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" t="n">
         <v>2</v>
@@ -7989,26 +7989,26 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - 122 Indonesia Investments, Holding Company for Indonesia's State-Owned M...</t>
+          <t>对外投资合作国别（地区）指南：泰国（2025年版） - 泰国（2025 年版） 寄语 泰国位于东盟中心位置，区位优势明显，社会总体较为稳定，政策透明度和贸易自 由化程度较高， 法律法规较为健全， 营商...</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="O116" t="n">
         <v>1</v>
@@ -8025,14 +8025,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>6</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>2</v>
@@ -8054,17 +8054,17 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -8090,14 +8090,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>7</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
         <v>2</v>
@@ -8119,26 +8119,26 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年度 - Evidence ID: TRD_003 Title: 中国对越南、泰国、马来西亚出口 HS 8541/8542（中间品），2018–2025年...</t>
+          <t>对外投资合作国别（地区）指南：印度（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>WTO_004</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -8184,26 +8184,26 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - cn/en/3688253/3689009/4180845/4821853/2023031716595159517. pdf https://w...</t>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - 122 Indonesia Investments, Holding Company for Indonesia's State-Owned M...</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -8220,17 +8220,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CASE_007</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>9</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -8249,26 +8249,26 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>华工正源：马来西亚工厂，公开表述为规避地缘风险 - 资讯 视频 6G 光通信 物联网 量子通信 卫星互联网 数智低空 Cloud&amp;AI 政策 运营商 设备商 终端 财经 市场 会展 直播 2026...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>C114通信网</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -8295,7 +8295,7 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -8314,26 +8314,26 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - 中国基金报记者 文夕 全球科技巨头持续加码算力，光模块环节厂商已成最大赢家之一。 7月14日，市值超1600亿元的全球光模块龙头中际旭创披露了一...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O124" t="n">
         <v>1</v>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -8574,12 +8574,12 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8589,11 +8589,11 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N125" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O125" t="n">
         <v>1</v>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
+          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>世界经济论坛（WEF）</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8654,11 +8654,11 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N126" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O126" t="n">
         <v>1</v>
@@ -8675,14 +8675,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>WTO_003</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
         <v>2</v>
@@ -8704,22 +8704,22 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） - 5 Summary Diversification 95% trade in no. of traded TL MFN AVG of Petro...</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N127" t="n">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
+          <t>对外投资合作国别（地区）指南：印度（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LI_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -8899,17 +8899,17 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Li Auto Inc. Form 20-F（fiscal year ended December 31, 2025）理想汽车2025财年年报 - Evidence ID: LI_001 Title: Li Auto Inc. Form 20-F（fiscal year ended Dece...</t>
+          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>理想汽车（Li Auto Inc.，SEC EDGAR）</t>
+          <t>中华人民共和国国务院</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -8935,14 +8935,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C131" t="n">
         <v>10</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
         <v>2</v>
@@ -8964,17 +8964,17 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -9308,7 +9308,7 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O136" t="n">
         <v>1</v>
@@ -9438,7 +9438,7 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O146" t="n">
         <v>1</v>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -10088,7 +10088,7 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O152" t="n">
         <v>1</v>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -10998,7 +10998,7 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O162" t="n">
         <v>1</v>
@@ -11193,7 +11193,7 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O165" t="n">
         <v>1</v>
@@ -11388,7 +11388,7 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -11499,17 +11499,17 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - . . . . . . . . . . . . . Effective with respect to entries on or after ...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -11535,14 +11535,14 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>ALB_001</t>
         </is>
       </c>
       <c r="C171" t="n">
         <v>10</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171" t="n">
         <v>2</v>
@@ -11564,17 +11564,17 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 - Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ...</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -11713,7 +11713,7 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O173" t="n">
         <v>1</v>
@@ -11908,7 +11908,7 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O176" t="n">
         <v>1</v>
@@ -11973,7 +11973,7 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -11990,14 +11990,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C178" t="n">
         <v>7</v>
       </c>
       <c r="D178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
@@ -12019,12 +12019,12 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N178" t="n">
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="P178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -12055,17 +12055,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>8</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -12084,26 +12084,26 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -12120,14 +12120,14 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C180" t="n">
         <v>9</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" t="n">
         <v>2</v>
@@ -12149,26 +12149,26 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -12185,17 +12185,17 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C181" t="n">
         <v>10</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -12214,32 +12214,32 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N181" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -12298,7 +12298,7 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O182" t="n">
         <v>1</v>
@@ -12445,17 +12445,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="C185" t="n">
         <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -12474,12 +12474,12 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -12489,17 +12489,17 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N185" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O185" t="n">
         <v>1</v>
       </c>
       <c r="P185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -12510,17 +12510,17 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="C186" t="n">
         <v>5</v>
       </c>
       <c r="D186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -12539,32 +12539,32 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） - Evidence ID: CASE_008 Title: 光模块厂商选择东南亚建厂以规避与欧美客户合作风险（中际旭创互动平台回复等） Publi...</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N186" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O186" t="n">
         <v>1</v>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -12575,14 +12575,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C187" t="n">
         <v>6</v>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E187" t="n">
         <v>2</v>
@@ -12604,17 +12604,17 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -12818,7 +12818,7 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -12835,17 +12835,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CASE_006</t>
+          <t>ALB_001</t>
         </is>
       </c>
       <c r="C191" t="n">
         <v>10</v>
       </c>
       <c r="D191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -12864,12 +12864,12 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>天孚通信：泰国一期投产、二期2025年投入使用 - 摘要 在过去几周的周报中，我们反复强调光模块行业正处于高景气周期，AI算力需求持续爆发推动高端光模块需求快速增长，供给将成为核心矛盾。 近期我们...</t>
+          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 - Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ...</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>国盛证券（经腾讯新闻转载）</t>
+          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12879,17 +12879,17 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N191" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
       </c>
       <c r="P191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -12948,7 +12948,7 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O192" t="n">
         <v>1</v>
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O195" t="n">
         <v>1</v>
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O196" t="n">
         <v>1</v>
@@ -13225,14 +13225,14 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>CASE_010</t>
+          <t>USMCA_001</t>
         </is>
       </c>
       <c r="C197" t="n">
         <v>6</v>
       </c>
       <c r="D197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E197" t="n">
         <v>2</v>
@@ -13254,12 +13254,12 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
+          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>美国白宫（经律所解读）</t>
+          <t>美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -13279,7 +13279,7 @@
         <v>0</v>
       </c>
       <c r="P197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -13290,14 +13290,14 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>USMCA_001</t>
+          <t>CASE_010</t>
         </is>
       </c>
       <c r="C198" t="n">
         <v>7</v>
       </c>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E198" t="n">
         <v>2</v>
@@ -13319,12 +13319,12 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>USMCA Chapter 4: Rules of Origin（美墨加协定第4章原产地规则） - Evidence ID: USMCA_001 Title: USMCA Chapter 4: Rules of Origin（美墨加协定第4章原...</t>
+          <t>白宫点名东南亚为非法转运高风险地区，并推出AI执法工具 - 审查应重点关注申报原产地是否得到适用法律标准和客观生产证据的支持。 公司应维护制造记录、物料清单、生产流程描述、供应商认证、采购订单、发票、路由...</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR）</t>
+          <t>美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -13338,13 +13338,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -13533,7 +13533,7 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -13728,7 +13728,7 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O204" t="n">
         <v>1</v>
@@ -14183,7 +14183,7 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -14248,7 +14248,7 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O212" t="n">
         <v>1</v>
@@ -14508,7 +14508,7 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O216" t="n">
         <v>1</v>
@@ -14573,7 +14573,7 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -14638,7 +14638,7 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -14768,7 +14768,7 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -14833,7 +14833,7 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -14944,12 +14944,12 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14963,7 +14963,7 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O223" t="n">
         <v>1</v>
@@ -15158,7 +15158,7 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O226" t="n">
         <v>1</v>
@@ -15223,7 +15223,7 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -15483,7 +15483,7 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -15873,7 +15873,7 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -15938,7 +15938,7 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -16198,7 +16198,7 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O242" t="n">
         <v>1</v>
@@ -16263,7 +16263,7 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O243" t="n">
         <v>1</v>
@@ -16328,7 +16328,7 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="O244" t="n">
         <v>1</v>
@@ -16345,14 +16345,14 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>WTO_002</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C245" t="n">
         <v>4</v>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E245" t="n">
         <v>2</v>
@@ -16374,26 +16374,26 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版） - 4. 投资环境 4.1 投资吸引力 马来西亚政府欢迎和鼓励外国投资者对其制造业及相关服务业进行投资，近年来一 直致力于改善投资环境、完善投资法律...</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O245" t="n">
         <v>1</v>
@@ -16410,14 +16410,14 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>WTO_003</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C246" t="n">
         <v>5</v>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E246" t="n">
         <v>2</v>
@@ -16439,26 +16439,26 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） - Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Impo...</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N246" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O246" t="n">
         <v>1</v>
@@ -16475,14 +16475,14 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="C247" t="n">
         <v>6</v>
       </c>
       <c r="D247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E247" t="n">
         <v>2</v>
@@ -16504,32 +16504,32 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N247" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
       </c>
       <c r="P247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -16569,12 +16569,12 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>国务院关于对外投资的规定（国务院令第837号） - 第六条第六条 国家健全海外综合服务体系，促进贸易投资⼀体化，完善公共平台与服务，统筹外事、法律、财税、⾦融、经贸、物流、出境⼊境、海关、贸促等领...</t>
+          <t>对外投资合作国别（地区）指南：泰国（2025年版） - 24 泰国（2025年版） 4. 投资环境 4.1 投资吸引力 泰国的竞争优势有：区位优势明显，位处东南亚地理中心；经济社会总体较稳定， 对华友...</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>中华人民共和国国务院</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -16588,7 +16588,7 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -16605,7 +16605,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -16634,12 +16634,12 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - Evidence ID: WEF_001 Title: Global Risks Report 2026（全球风险报告2026，第21版） Pu...</t>
+          <t>The art, science, and technology of geopolitical scenario planning - Evidence ID: MCK_001 Title: The art, science, and technology of geopolit...</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>麦肯锡（McKinsey）</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -16649,11 +16649,11 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N249" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -16670,7 +16670,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -16699,12 +16699,12 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
+          <t>对外投资合作国别（地区）指南：印度（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -16718,7 +16718,7 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>WTO_003</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -16764,12 +16764,12 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>WTO Tariff Profile: India — Tariffs and Imports Summary（WTO国别关税快照：印度） - Evidence ID: WTO_003 Title: WTO Tariff Profile: India — Tariffs and Impo...</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -16783,7 +16783,7 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>CASE_009</t>
+          <t>BIS_001</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
+          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>BIS_001</t>
+          <t>CASE_009</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -16959,7 +16959,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Expansion of End-User Controls to Cover Affiliates of Certain Listed Entities（关联企业规则 / 50%穿透规则，临时最终规则） - Evidence ID: BIS_001 Title: Expansion of End-User Controls to Cover Affi...</t>
+          <t>BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 - Evidence ID: CASE_009 Title: BIS 50%穿透规则：发布→暂停→2026-11-10恢复的完整时间线 Publis...</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O254" t="n">
         <v>1</v>
@@ -17173,7 +17173,7 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -17303,7 +17303,7 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -17320,14 +17320,14 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C260" t="n">
         <v>9</v>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E260" t="n">
         <v>2</v>
@@ -17349,17 +17349,17 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -17385,14 +17385,14 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C261" t="n">
         <v>10</v>
       </c>
       <c r="D261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E261" t="n">
         <v>2</v>
@@ -17414,17 +17414,17 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -17433,7 +17433,7 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -17823,7 +17823,7 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -17953,7 +17953,7 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -18083,7 +18083,7 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -18148,7 +18148,7 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O272" t="n">
         <v>1</v>
@@ -18360,14 +18360,14 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>CASE_003</t>
+          <t>DOC_001</t>
         </is>
       </c>
       <c r="C276" t="n">
         <v>5</v>
       </c>
       <c r="D276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E276" t="n">
         <v>2</v>
@@ -18389,12 +18389,12 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
+          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>美国商务部</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -18414,7 +18414,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -18425,14 +18425,14 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>DOC_001</t>
+          <t>CASE_003</t>
         </is>
       </c>
       <c r="C277" t="n">
         <v>6</v>
       </c>
       <c r="D277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E277" t="n">
         <v>2</v>
@@ -18454,12 +18454,12 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Final Circumvention Determinations: Crystalline Silicon Photovoltaic Cells from Cambodia, Malaysia, Thailand and Vietnam（东南亚四国光伏反规避终裁） - Evidence ID: DOC_001 Title: Final Circumvention Determinations: Crystall...</t>
+          <t>同一反规避调查中被认定“未规避”的企业（Hanwha、Jinko马来西亚、Boviet越南） - Importers and consumers of solar panels should review their supply chain...</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>美国商务部</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -18473,13 +18473,13 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -18603,7 +18603,7 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -18733,7 +18733,7 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -18798,7 +18798,7 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O282" t="n">
         <v>1</v>
@@ -18815,7 +18815,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>WTO_002</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -18863,7 +18863,7 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="O283" t="n">
         <v>1</v>
@@ -18880,7 +18880,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Evidence ID: WTO_001 Title: Global Trade Outlook and Statistics（2026年3月版...</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -18928,7 +18928,7 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="O284" t="n">
         <v>1</v>
@@ -18993,7 +18993,7 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="O285" t="n">
         <v>1</v>
@@ -19010,14 +19010,14 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C286" t="n">
         <v>5</v>
       </c>
       <c r="D286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E286" t="n">
         <v>2</v>
@@ -19039,12 +19039,12 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
+          <t>对外投资合作国别（地区）指南：印度（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>联合国贸易和发展会议（UNCTAD）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -19054,17 +19054,17 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N286" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O286" t="n">
         <v>1</v>
       </c>
       <c r="P286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -19075,14 +19075,14 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C287" t="n">
         <v>6</v>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E287" t="n">
         <v>2</v>
@@ -19104,12 +19104,12 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
+          <t>World Investment Report 2026: International Investment in a Turbulent Era - Evidence ID: UNCTAD_001 Title: World Investment Report 2026: Internation...</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>联合国贸易和发展会议（UNCTAD）</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -19119,17 +19119,17 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N287" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
       </c>
       <c r="P287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -19169,26 +19169,26 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Global Risks Report 2026（全球风险报告2026，第21版） - recession, stagnation) 02 nd Geoeconomic confrontation (sanctions, tarif...</t>
+          <t>Regulation (EU) 2019/452 establishing a framework for the screening of foreign direct investments into the Union（欧盟外资安全审查框架条例） - Evidence ID: EU_004 Title: Regulation (EU) 2019/452 establishing a frame...</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N288" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -19205,14 +19205,14 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C289" t="n">
         <v>8</v>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E289" t="n">
         <v>2</v>
@@ -19234,32 +19234,32 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>The art, science, and technology of geopolitical scenario planning - McKinsey &amp; Company Specialist advisory support Clearer regulatory guidan...</t>
+          <t>对外投资合作国别（地区）指南：马来西亚（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和 二十届历次全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>麦肯锡（McKinsey）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N289" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
       </c>
       <c r="P289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -19270,17 +19270,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>CASE_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C290" t="n">
         <v>9</v>
       </c>
       <c r="D290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -19299,26 +19299,26 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
+          <t>对外投资合作国别（地区）指南：越南（2025年版） - 商务部以习近平新时代中国特色社会主义思想为指导，深入学习贯彻党的二十大和二十届历次 全会精神，按照党的二十届四中全会决策部署，有效实施对外投资管...</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>路透社（Reuters）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N290" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -19335,17 +19335,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>KPMG_001</t>
+          <t>CASE_001</t>
         </is>
       </c>
       <c r="C291" t="n">
         <v>10</v>
       </c>
       <c r="D291" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E291" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -19364,12 +19364,12 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>KPMG 2026 US Supply Chain Survey - Evidence ID: KPMG_001 Title: KPMG 2026 US Supply Chain Survey Publisher:...</t>
+          <t>Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 - Evidence ID: CASE_001 Title: Dawang Metals：客户订单转移印度后回流，企业放弃海外建厂 Publishe...</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>毕马威（KPMG）</t>
+          <t>路透社（Reuters）</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -19379,17 +19379,17 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="N291" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
       </c>
       <c r="P291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -19513,7 +19513,7 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O293" t="n">
         <v>1</v>
@@ -19643,7 +19643,7 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O295" t="n">
         <v>1</v>
@@ -19708,7 +19708,7 @@
         </is>
       </c>
       <c r="N296" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O296" t="n">
         <v>1</v>
@@ -19968,7 +19968,7 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O302" t="n">
         <v>1</v>
@@ -20163,7 +20163,7 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O303" t="n">
         <v>1</v>
@@ -20180,7 +20180,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -20209,17 +20209,17 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -20310,7 +20310,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -20339,17 +20339,17 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -20488,7 +20488,7 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O308" t="n">
         <v>0</v>
@@ -20618,7 +20618,7 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O310" t="n">
         <v>0</v>
@@ -20683,7 +20683,7 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O311" t="n">
         <v>0</v>
@@ -20748,7 +20748,7 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O312" t="n">
         <v>1</v>
@@ -20813,7 +20813,7 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="O313" t="n">
         <v>1</v>
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O315" t="n">
         <v>1</v>
@@ -21203,7 +21203,7 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O319" t="n">
         <v>0</v>
@@ -21333,7 +21333,7 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O321" t="n">
         <v>0</v>
@@ -21398,7 +21398,7 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O322" t="n">
         <v>1</v>
@@ -21545,7 +21545,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -21555,7 +21555,7 @@
         <v>1</v>
       </c>
       <c r="E325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
@@ -21574,26 +21574,26 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N325" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O325" t="n">
         <v>1</v>
@@ -21610,17 +21610,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C326" t="n">
         <v>5</v>
       </c>
       <c r="D326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
@@ -21639,26 +21639,26 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - _x_tr_sch=http&amp;_x_tr_sl=auto&amp;_x_tr_tl=en&amp;_x_tr_hl=en&amp;_x_tr_pto=wapp Appe...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N326" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O326" t="n">
         <v>1</v>
@@ -21675,14 +21675,14 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C327" t="n">
         <v>6</v>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E327" t="n">
         <v>2</v>
@@ -21704,22 +21704,22 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - _x_tr_sch=http&amp;_x_tr_sl=auto&amp;_x_tr_tl=en&amp;_x_tr_hl=en&amp;_x_tr_pto=wapp Appe...</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N327" t="n">
@@ -21740,14 +21740,14 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>WTO_002</t>
         </is>
       </c>
       <c r="C328" t="n">
         <v>7</v>
       </c>
       <c r="D328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E328" t="n">
         <v>2</v>
@@ -21769,26 +21769,26 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N328" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O328" t="n">
         <v>0</v>
@@ -21805,14 +21805,14 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>WTO_002</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C329" t="n">
         <v>8</v>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E329" t="n">
         <v>2</v>
@@ -21834,22 +21834,22 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — India（WT/TPR/S/403）印度第七次贸易政策审议秘书处报告 - Evidence ID: WTO_002 Title: Trade Policy Review: Report by the Secretari...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N329" t="n">
@@ -21918,7 +21918,7 @@
         </is>
       </c>
       <c r="N330" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O330" t="n">
         <v>0</v>
@@ -22048,7 +22048,7 @@
         </is>
       </c>
       <c r="N332" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O332" t="n">
         <v>1</v>
@@ -22113,7 +22113,7 @@
         </is>
       </c>
       <c r="N333" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O333" t="n">
         <v>1</v>
@@ -22373,7 +22373,7 @@
         </is>
       </c>
       <c r="N337" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O337" t="n">
         <v>0</v>
@@ -22438,7 +22438,7 @@
         </is>
       </c>
       <c r="N338" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O338" t="n">
         <v>0</v>
@@ -22503,7 +22503,7 @@
         </is>
       </c>
       <c r="N339" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O339" t="n">
         <v>0</v>
@@ -22520,7 +22520,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>WTO_001</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -22530,7 +22530,7 @@
         <v>1</v>
       </c>
       <c r="E340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -22549,22 +22549,22 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+          <t>Global Trade Outlook and Statistics（2026年3月版） - Between 28 February and 9 March 2026, the ongoing regional conflict led ...</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N340" t="n">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>WTO_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -22595,7 +22595,7 @@
         <v>1</v>
       </c>
       <c r="E341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
@@ -22614,22 +22614,22 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>Global Trade Outlook and Statistics（2026年3月版） - Between 28 February and 9 March 2026, the ongoing regional conflict led ...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N341" t="n">
@@ -22698,7 +22698,7 @@
         </is>
       </c>
       <c r="N342" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O342" t="n">
         <v>1</v>
@@ -22763,7 +22763,7 @@
         </is>
       </c>
       <c r="N343" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O343" t="n">
         <v>1</v>
@@ -22845,7 +22845,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -22874,17 +22874,17 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -22893,7 +22893,7 @@
         </is>
       </c>
       <c r="N345" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O345" t="n">
         <v>1</v>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -22939,17 +22939,17 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -23023,7 +23023,7 @@
         </is>
       </c>
       <c r="N347" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O347" t="n">
         <v>0</v>
@@ -23088,7 +23088,7 @@
         </is>
       </c>
       <c r="N348" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O348" t="n">
         <v>0</v>
@@ -23105,7 +23105,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>IEA_001</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -23115,7 +23115,7 @@
         <v>0</v>
       </c>
       <c r="E349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
@@ -23134,12 +23134,12 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - After unwinding its joint venture with Ford and moving to sole operation...</t>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - These additional export costs are prompting Chinese OEMs to establish ne...</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>国际能源署（IEA）</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -23149,11 +23149,11 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N349" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O349" t="n">
         <v>0</v>
@@ -23170,7 +23170,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>IEA_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -23180,7 +23180,7 @@
         <v>0</v>
       </c>
       <c r="E350" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
@@ -23199,12 +23199,12 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>Global EV Outlook 2025（全球电动汽车展望2025） - These additional export costs are prompting Chinese OEMs to establish ne...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - After unwinding its joint venture with Ford and moving to sole operation...</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>国际能源署（IEA）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -23214,11 +23214,11 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N350" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O350" t="n">
         <v>0</v>
@@ -23348,7 +23348,7 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O352" t="n">
         <v>1</v>
@@ -23365,14 +23365,14 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>DHS_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C353" t="n">
         <v>2</v>
       </c>
       <c r="D353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E353" t="n">
         <v>2</v>
@@ -23394,17 +23394,17 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>美国国土安全部（DHS，Federal Register）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>劳工</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -23430,14 +23430,14 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>IRS_001</t>
+          <t>DHS_001</t>
         </is>
       </c>
       <c r="C354" t="n">
         <v>3</v>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E354" t="n">
         <v>2</v>
@@ -23459,17 +23459,17 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
+          <t>Notice Regarding the Uyghur Forced Labor Prevention Act Entity List（UFLPA 实体清单更新公告） - Evidence ID: DHS_001 Title: Notice Regarding the Uyghur Forced Labor Pre...</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>美国财政部/国税局（Federal Register）</t>
+          <t>美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>劳工</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -23543,7 +23543,7 @@
         </is>
       </c>
       <c r="N355" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O355" t="n">
         <v>1</v>
@@ -23673,7 +23673,7 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O357" t="n">
         <v>0</v>
@@ -23738,7 +23738,7 @@
         </is>
       </c>
       <c r="N358" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O358" t="n">
         <v>0</v>
@@ -23755,14 +23755,14 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="C359" t="n">
         <v>8</v>
       </c>
       <c r="D359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E359" t="n">
         <v>2</v>
@@ -23784,17 +23784,17 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -23820,14 +23820,14 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C360" t="n">
         <v>9</v>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E360" t="n">
         <v>2</v>
@@ -23849,17 +23849,17 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -23868,7 +23868,7 @@
         </is>
       </c>
       <c r="N360" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O360" t="n">
         <v>0</v>
@@ -23998,7 +23998,7 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O362" t="n">
         <v>1</v>
@@ -24128,7 +24128,7 @@
         </is>
       </c>
       <c r="N364" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O364" t="n">
         <v>1</v>
@@ -24210,7 +24210,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>IEA_001</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -24220,7 +24220,7 @@
         <v>1</v>
       </c>
       <c r="E366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
@@ -24239,12 +24239,12 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>国际能源署（IEA）</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -24254,7 +24254,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N366" t="n">
@@ -24275,7 +24275,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>IEA_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -24285,7 +24285,7 @@
         <v>1</v>
       </c>
       <c r="E367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
@@ -24304,12 +24304,12 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>国际能源署（IEA）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -24319,11 +24319,11 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N367" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O367" t="n">
         <v>0</v>
@@ -24388,7 +24388,7 @@
         </is>
       </c>
       <c r="N368" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O368" t="n">
         <v>0</v>
@@ -24453,7 +24453,7 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O369" t="n">
         <v>0</v>
@@ -24518,7 +24518,7 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O370" t="n">
         <v>0</v>
@@ -24535,14 +24535,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C371" t="n">
         <v>10</v>
       </c>
       <c r="D371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E371" t="n">
         <v>2</v>
@@ -24564,22 +24564,22 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The cost of not knowing is rising faster than the cost of ﬁnding out, an...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N371" t="n">
@@ -24713,7 +24713,7 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O373" t="n">
         <v>1</v>
@@ -24778,7 +24778,7 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O374" t="n">
         <v>1</v>
@@ -24860,14 +24860,14 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>TSLA_001</t>
         </is>
       </c>
       <c r="C376" t="n">
         <v>5</v>
       </c>
       <c r="D376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E376" t="n">
         <v>2</v>
@@ -24889,17 +24889,17 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -24925,14 +24925,14 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>TSLA_001</t>
+          <t>MOFCOM_002</t>
         </is>
       </c>
       <c r="C377" t="n">
         <v>6</v>
       </c>
       <c r="D377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E377" t="n">
         <v>2</v>
@@ -24954,17 +24954,17 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>Tesla, Inc. Form 10-K（fiscal year ended December 31, 2025）特斯拉2025财年年报 - Evidence ID: TSLA_001 Title: Tesla, Inc. Form 10-K（fiscal year ended Dec...</t>
+          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>商务部</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>出口管制</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O377" t="n">
         <v>0</v>
@@ -25168,7 +25168,7 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O380" t="n">
         <v>0</v>
@@ -25185,7 +25185,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -25214,22 +25214,22 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N381" t="n">
@@ -25428,7 +25428,7 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O384" t="n">
         <v>1</v>
@@ -25493,7 +25493,7 @@
         </is>
       </c>
       <c r="N385" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O385" t="n">
         <v>1</v>
@@ -25558,7 +25558,7 @@
         </is>
       </c>
       <c r="N386" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O386" t="n">
         <v>1</v>
@@ -25623,7 +25623,7 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O387" t="n">
         <v>0</v>
@@ -25753,7 +25753,7 @@
         </is>
       </c>
       <c r="N389" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O389" t="n">
         <v>0</v>
@@ -25818,7 +25818,7 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O390" t="n">
         <v>0</v>
@@ -25883,7 +25883,7 @@
         </is>
       </c>
       <c r="N391" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O391" t="n">
         <v>0</v>
@@ -25948,7 +25948,7 @@
         </is>
       </c>
       <c r="N392" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O392" t="n">
         <v>1</v>
@@ -26013,7 +26013,7 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O393" t="n">
         <v>1</v>
@@ -26078,7 +26078,7 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O394" t="n">
         <v>1</v>
@@ -26095,14 +26095,14 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>WTO_004</t>
         </is>
       </c>
       <c r="C395" t="n">
         <v>4</v>
       </c>
       <c r="D395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E395" t="n">
         <v>2</v>
@@ -26124,32 +26124,32 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
+          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretari...</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N395" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O395" t="n">
         <v>1</v>
       </c>
       <c r="P395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396">
@@ -26160,14 +26160,14 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C396" t="n">
         <v>5</v>
       </c>
       <c r="D396" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E396" t="n">
         <v>2</v>
@@ -26189,22 +26189,22 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>Trade Policy Review: Report by the Secretariat — Indonesia（WT/TPR/S/401）印尼第七次贸易政策审议秘书处报告 - Evidence ID: WTO_004 Title: Trade Policy Review: Report by the Secretari...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - Evidence ID: WH_002 Title: The Great Transshipment Scam: Rise, Scope, an...</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>本地化政策</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N396" t="n">
@@ -26214,7 +26214,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>CASE_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -26319,17 +26319,17 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>反规避</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
@@ -26338,7 +26338,7 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O398" t="n">
         <v>0</v>
@@ -26355,7 +26355,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>CASE_002</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -26384,17 +26384,17 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 - Evidence ID: CASE_002 Title: 美国对东南亚四国光伏产品反规避认定：视为中国原产并适用对华双反 Publisher: ...</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>美国商务部（经律所解读）</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>反规避</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
@@ -26468,7 +26468,7 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O400" t="n">
         <v>0</v>
@@ -26533,7 +26533,7 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O401" t="n">
         <v>0</v>
@@ -26598,7 +26598,7 @@
         </is>
       </c>
       <c r="N402" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O402" t="n">
         <v>1</v>
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="N404" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O404" t="n">
         <v>1</v>
@@ -26810,7 +26810,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>IEA_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -26839,26 +26839,26 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>国际能源署（IEA）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N406" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O406" t="n">
         <v>1</v>
@@ -26875,14 +26875,14 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>CSIS_001</t>
+          <t>IEA_001</t>
         </is>
       </c>
       <c r="C407" t="n">
         <v>6</v>
       </c>
       <c r="D407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E407" t="n">
         <v>2</v>
@@ -26904,22 +26904,22 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The EV battery example shows the problem that a product passport is desi...</t>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>战略与国际研究中心（CSIS）</t>
+          <t>国际能源署（IEA）</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N407" t="n">
@@ -26940,14 +26940,14 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>CSIS_001</t>
         </is>
       </c>
       <c r="C408" t="n">
         <v>7</v>
       </c>
       <c r="D408" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E408" t="n">
         <v>2</v>
@@ -26969,26 +26969,26 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+          <t>The Visibility Gap: How AI Can Stop Chinese Transshipment Under USMCA - The EV battery example shows the problem that a product passport is desi...</t>
         </is>
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>战略与国际研究中心（CSIS）</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N408" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O408" t="n">
         <v>0</v>
@@ -27053,7 +27053,7 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O409" t="n">
         <v>0</v>
@@ -27118,7 +27118,7 @@
         </is>
       </c>
       <c r="N410" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O410" t="n">
         <v>0</v>
@@ -27248,7 +27248,7 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O412" t="n">
         <v>1</v>
@@ -27395,7 +27395,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>UST_001</t>
+          <t>TRD_001</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -27424,26 +27424,26 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
+          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>美国贸易代表办公室（USTR，Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>贸易流</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N415" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O415" t="n">
         <v>1</v>
@@ -27460,7 +27460,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>TRD_001</t>
+          <t>UST_001</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -27489,26 +27489,26 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–2025年度 - Evidence ID: TRD_001 Title: 美国自中国、越南、泰国、马来西亚进口 HS 870380, 850760，2018–20...</t>
+          <t>Notice of Modification: China's Acts, Policies and Practices Related to Technology Transfer, Intellectual Property and Innovation（Section 301 对华关税调整通知） - Evidence ID: UST_001 Title: Notice of Modification: China's Acts, Polici...</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国贸易代表办公室（USTR，Federal Register）</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>贸易流</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>S</t>
         </is>
       </c>
       <c r="N416" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O416" t="n">
         <v>1</v>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>IEA_001</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -27535,7 +27535,7 @@
         <v>0</v>
       </c>
       <c r="E417" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G417" t="inlineStr">
         <is>
@@ -27554,12 +27554,12 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>国际能源署（IEA）</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -27569,7 +27569,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N417" t="n">
@@ -27590,7 +27590,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>IEA_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -27600,7 +27600,7 @@
         <v>0</v>
       </c>
       <c r="E418" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G418" t="inlineStr">
         <is>
@@ -27619,12 +27619,12 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>国际能源署（IEA）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -27634,11 +27634,11 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N418" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O418" t="n">
         <v>0</v>
@@ -27703,7 +27703,7 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O419" t="n">
         <v>0</v>
@@ -27720,14 +27720,14 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>EU_001</t>
         </is>
       </c>
       <c r="C420" t="n">
         <v>9</v>
       </c>
       <c r="D420" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E420" t="n">
         <v>2</v>
@@ -27749,17 +27749,17 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - As illustrated by these pairings, when China-origin goods enter the U. S...</t>
+          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>市场准入</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -27768,7 +27768,7 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O420" t="n">
         <v>0</v>
@@ -27785,14 +27785,14 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>EU_001</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C421" t="n">
         <v>10</v>
       </c>
       <c r="D421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E421" t="n">
         <v>2</v>
@@ -27814,17 +27814,17 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>Regulation (EU) 2023/1542 concerning batteries and waste batteries（欧盟电池与废电池法规） - Evidence ID: EU_001 Title: Regulation (EU) 2023/1542 concerning batterie...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - As illustrated by these pairings, when China-origin goods enter the U. S...</t>
         </is>
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>市场准入</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -27833,7 +27833,7 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O421" t="n">
         <v>0</v>
@@ -27963,7 +27963,7 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="O423" t="n">
         <v>1</v>
@@ -28093,7 +28093,7 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O425" t="n">
         <v>1</v>
@@ -28110,7 +28110,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>EU_003</t>
+          <t>WH_002</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -28139,17 +28139,17 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
+          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - They are product-to-industry matches: foreign corridors handling high-ri...</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>关税</t>
+          <t>原产地与转运</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>WH_002</t>
+          <t>EU_003</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -28204,17 +28204,17 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>The Great Transshipment Scam: Rise, Scope, and Costs（白宫非法转运报告） - They are product-to-industry matches: foreign corridors handling high-ri...</t>
+          <t>Commission Implementing Regulation (EU) 2024/2754 imposing a definitive countervailing duty on imports of new battery electric vehicles originating in China（对华纯电动车最终反补贴税） - Evidence ID: EU_003 Title: Commission Implementing Regulation (EU) 2024/...</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室</t>
+          <t>欧盟委员会（EUR-Lex / Official Journal）</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>原产地与转运</t>
+          <t>关税</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -28240,7 +28240,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>SNE_001</t>
+          <t>IEA_001</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -28250,7 +28250,7 @@
         <v>0</v>
       </c>
       <c r="E428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>
@@ -28269,12 +28269,12 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
+          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
         </is>
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>SNE Research</t>
+          <t>国际能源署（IEA）</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="N428" t="n">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>MOFCOM_002</t>
+          <t>ALB_001</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -28334,17 +28334,17 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物项出口管制） - Evidence ID: MOFCOM_002 Title: 商务部公告2025年第72号（暂停实施2024年第46号公告第二款，涉及对美两用物...</t>
+          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 - Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ...</t>
         </is>
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>商务部</t>
+          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
         </is>
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>出口管制</t>
+          <t>供应链布局</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -28370,7 +28370,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>ALB_001</t>
+          <t>IRS_001</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -28399,17 +28399,17 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>Albemarle Corporation Form 10-K（fiscal year ended December 31, 2025）雅保2025财年年报 - Evidence ID: ALB_001 Title: Albemarle Corporation Form 10-K（fiscal year ...</t>
+          <t>Clean Vehicle Credits Under Sections 25E and 30D; Transfer of Credits; Critical Minerals and Battery Components; Foreign Entities of Concern（清洁车辆抵免与FEOC最终规则） - Evidence ID: IRS_001 Title: Clean Vehicle Credits Under Sections 25E and...</t>
         </is>
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+          <t>美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>供应链布局</t>
+          <t>本地化政策</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>IEA_001</t>
+          <t>SNE_001</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -28445,7 +28445,7 @@
         <v>0</v>
       </c>
       <c r="E431" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G431" t="inlineStr">
         <is>
@@ -28464,12 +28464,12 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>Global EV Outlook 2025（全球电动汽车展望2025） - Evidence ID: IEA_001 Title: Global EV Outlook 2025（全球电动汽车展望2025） Publish...</t>
+          <t>January-August 2026 Global EV Battery Usage Reaches 844.2 GWh, Up 19.7% Year-on-Year（2026年1–8月全球动力电池装车量快报） - Evidence ID: SNE_001 Title: January-August 2026 Global EV Battery Usage ...</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>国际能源署（IEA）</t>
+          <t>SNE Research</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -28479,11 +28479,11 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="N431" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O431" t="n">
         <v>0</v>
@@ -28662,7 +28662,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CASE_005; CASE_004; CASE_001; CASE_006; IEA_001; CASE_008; CASE_007; WB_001; TRD_001; EU_003</t>
+          <t>CASE_005; CASE_004; CASE_001; CASE_006; IEA_001; CASE_008; CASE_007; WB_001; EU_003; TRD_001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -28743,7 +28743,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_010; IEA_001; WH_002; CASE_003; CASE_002; TRD_003; WB_001; TRD_001; CASE_001</t>
+          <t>CASE_007; CASE_010; IEA_001; WH_002; CASE_003; CASE_002; TRD_003; WB_001; TRD_001; WTO_004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -28770,10 +28770,10 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O3" t="n">
         <v>0.9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.95</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -28782,11 +28782,11 @@
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>IEA_001</t>
+          <t>IEA_001; WTO_004</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -28976,7 +28976,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; DHS_001; CASE_001; SNE_001; WH_002; CASE_010; IEA_001; CASE_008</t>
+          <t>CASE_003; CASE_002; DOC_001; DHS_001; WH_002; CASE_001; SNE_001; CASE_010; ALB_001; IEA_001</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -29003,10 +29003,10 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -29015,15 +29015,15 @@
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>DHS_001; CASE_001; SNE_001; WH_002; CASE_010; IEA_001</t>
+          <t>DHS_001; WH_002; CASE_001; SNE_001; CASE_010; ALB_001; IEA_001</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; CASE_003; USMCA_001; TRD_001; DHS_001; TRD_003</t>
+          <t>CASE_010; WH_002; WH_001; CASE_002; CSIS_001; USMCA_001; CASE_003; TRD_001; DHS_001; TRD_003</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -29369,7 +29369,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_001; USMCA_001; WH_002; DHS_001; CSIS_001; TRD_003</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; USMCA_001; WH_001; WH_002; DHS_001; TRD_003; CSIS_001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -29446,7 +29446,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; UNCTAD_001; CASE_001; DHS_001; SNE_001; MCK_001; IRS_001; WEF_001; EU_003</t>
+          <t>MOFCOM_005; MOFCOM_003; CNGOV_001; MOFCOM_006; MOFCOM_004; IMF_001; UNCTAD_001; CASE_001; DHS_001; SNE_001</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -29455,28 +29455,28 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
         <v>0.6</v>
       </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.4</v>
-      </c>
       <c r="O12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -29485,15 +29485,15 @@
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; CASE_001; DHS_001; MCK_001; WEF_001</t>
+          <t>IMF_001; UNCTAD_001; CASE_001; DHS_001</t>
         </is>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WEF_001; WTO_002; UNCTAD_001; CNGOV_001; WTO_004; DHS_001; TRD_003; EU_003; CASE_007; CASE_008</t>
+          <t>WEF_001; WTO_002; MOFCOM_003; UNCTAD_001; MOFCOM_006; MOFCOM_004; MOFCOM_005; WTO_004; CNGOV_001; DHS_001</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -29539,7 +29539,7 @@
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
@@ -29560,7 +29560,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>WEF_001; WTO_002; UNCTAD_001; CNGOV_001; WTO_004; DHS_001; TRD_003; EU_003; CASE_007; CASE_008</t>
+          <t>WEF_001; WTO_002; MOFCOM_003; UNCTAD_001; MOFCOM_006; MOFCOM_004; MOFCOM_005; WTO_004; CNGOV_001; DHS_001</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -29598,7 +29598,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; WEF_001; MCK_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; CNGOV_001; EU_004</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -29631,7 +29631,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>IMF_001; UNCTAD_001; WTO_001; WEF_001; MCK_001; WTO_003; CNGOV_001; EU_004; LI_001; TSLA_001</t>
+          <t>IMF_001; UNCTAD_001; WTO_001; MCK_001; WEF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; CNGOV_001; EU_004</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; DHS_001; USMCA_001; WH_001; UST_001; CASE_002</t>
+          <t>TRD_003; CASE_010; WH_002; WTO_001; CSIS_001; DHS_001; USMCA_001; WH_001; CASE_002; ALB_001</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -29931,10 +29931,10 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O18" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -29943,11 +29943,11 @@
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>WTO_001; DHS_001; UST_001</t>
+          <t>WTO_001; DHS_001</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -29985,7 +29985,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CASE_002; TRD_003; CASE_008; DHS_001; TSLA_001; EU_003; CASE_001; SNE_001; IRS_001; TRD_001</t>
+          <t>CASE_002; TRD_003; CASE_008; DHS_001; TSLA_001; EU_003; SNE_001; IRS_001; TRD_001; CASE_001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -30066,22 +30066,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_003; CASE_007; CASE_004; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; TSLA_001; CASE_008; DHS_001; CASE_003; CASE_007; CASE_004; ALB_001</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_006; CASE_008; KPMG_001</t>
+          <t>CASE_001; CASE_004; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
@@ -30099,7 +30099,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>CASE_001; KPMG_001; SNE_001; CASE_008; DHS_001; TSLA_001; CASE_003; CASE_007; CASE_004; CASE_006</t>
+          <t>CASE_001; KPMG_001; SNE_001; TSLA_001; CASE_008; DHS_001; CASE_003; CASE_007; CASE_004; ALB_001</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -30137,7 +30137,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRD_003; WH_002; WTO_001; TRD_001; CSIS_001; CASE_010; USMCA_001; WH_001; DHS_001; IEA_001</t>
+          <t>TRD_003; WH_002; WTO_001; TRD_001; CSIS_001; USMCA_001; CASE_010; WH_001; DHS_001; IEA_001</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -30376,7 +30376,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; WH_002; CASE_010; USMCA_001; CSIS_001; WH_001; DHS_001; EU_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010; USMCA_001; CSIS_001; WH_001; DHS_001; EU_001</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -30538,22 +30538,22 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MOFCOM_004; MOFCOM_003; WTO_002; MOFCOM_006; MCK_001; MOFCOM_005; WTO_003</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>IMF_001; MCK_001; UNCTAD_001; WEF_001; WTO_001</t>
+          <t>IMF_001; MCK_001; UNCTAD_001; WTO_001</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -30571,7 +30571,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>UNCTAD_001; WTO_001; IMF_001; WTO_002; WTO_003; MCK_001; CNGOV_001; WEF_001; EU_004; TRD_001</t>
+          <t>UNCTAD_001; WTO_001; IMF_001; MOFCOM_004; MOFCOM_003; WTO_002; MOFCOM_006; MCK_001; MOFCOM_005; WTO_003</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -30609,7 +30609,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BIS_002; CASE_009; BIS_001; FR_001; DHS_001; NIO_001; CASE_001; XPEV_001; MOFCOM_002; IRS_001</t>
+          <t>BIS_002; BIS_001; CASE_009; FR_001; DHS_001; NIO_001; CASE_001; XPEV_001; IRS_001; MOFCOM_002</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -30763,7 +30763,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_002; WH_002; CASE_010; CASE_003; DOC_001; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
+          <t>TRD_003; CASE_002; WH_002; CASE_010; DOC_001; CASE_003; CSIS_001; WTO_001; DHS_001; USMCA_001</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -30772,10 +30772,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>CASE_003; DOC_001; WTO_001; DHS_001</t>
+          <t>DOC_001; CASE_003; WTO_001; DHS_001</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -30844,22 +30844,22 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001; EU_004; WEF_001; MCK_001; CASE_001; KPMG_001</t>
+          <t>IMF_001; WTO_001; WTO_002; CNGOV_001; MOFCOM_005; UNCTAD_001; EU_004; MOFCOM_004; MOFCOM_003; CASE_001</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; KPMG_001; MCK_001; UNCTAD_001</t>
+          <t>CNGOV_001; IMF_001; UNCTAD_001</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
         <v>0.6</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>IMF_001; WTO_002; WTO_001; CNGOV_001; UNCTAD_001; EU_004; WEF_001; MCK_001; CASE_001; KPMG_001</t>
+          <t>IMF_001; WTO_001; WTO_002; CNGOV_001; MOFCOM_005; UNCTAD_001; EU_004; MOFCOM_004; MOFCOM_003; CASE_001</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TSLA_001; EU_003; DHS_001; WH_002; UST_001; SNE_001; IEA_001; CSIS_001; TRD_001; IRS_001</t>
+          <t>TSLA_001; EU_003; UST_001; WH_002; DHS_001; SNE_001; IEA_001; CSIS_001; TRD_001; IRS_001</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -31154,7 +31154,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; WH_002; SNE_001; EU_003; TRD_001; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
+          <t>ALB_001; DHS_001; WH_002; TRD_001; SNE_001; EU_003; WTO_002; MOFCOM_002; IRS_001; CASE_003</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -31166,7 +31166,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
@@ -31187,7 +31187,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>ALB_001; DHS_001; WH_002; SNE_001; EU_003; TRD_001; MOFCOM_002; WTO_002; IRS_001; CASE_003</t>
+          <t>ALB_001; DHS_001; WH_002; TRD_001; SNE_001; EU_003; WTO_002; MOFCOM_002; IRS_001; CASE_003</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -31225,7 +31225,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>USMCA_001; WH_002; CASE_002; DHS_001; CSIS_001; UST_001; EU_003; IRS_001; SNE_001; WTO_001</t>
+          <t>USMCA_001; WH_002; CASE_002; DHS_001; CSIS_001; UST_001; EU_003; IRS_001; WTO_001; SNE_001</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -31306,7 +31306,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WTO_002; WTO_003; WH_002; DHS_001; IRS_001; UST_001; WTO_004; SNE_001; IEA_001; ITA_001</t>
+          <t>WTO_002; WTO_003; WH_002; IRS_001; DHS_001; UST_001; WTO_004; IEA_001; SNE_001; ITA_001</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -31349,7 +31349,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>WH_002; DHS_001; IRS_001; WTO_004; SNE_001; ITA_001</t>
+          <t>WH_002; IRS_001; DHS_001; WTO_004; SNE_001; ITA_001</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -31387,7 +31387,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WTO_004; DHS_001; IRS_001; EU_001; SNE_001; EU_003; WTO_002; MOFCOM_002; TSLA_001; EU_002</t>
+          <t>WTO_004; IRS_001; DHS_001; EU_001; SNE_001; EU_003; WTO_002; TSLA_001; MOFCOM_002; EU_002</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WB_001; DHS_001; TRD_001; CASE_002; SNE_001; IEA_001; TSLA_001; ALB_001; EU_003; CSIS_001</t>
+          <t>WB_001; DHS_001; TRD_001; CASE_002; IEA_001; SNE_001; TSLA_001; ALB_001; EU_003; UST_001</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -31507,11 +31507,11 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>DHS_001; TSLA_001; CSIS_001</t>
+          <t>DHS_001; TSLA_001; UST_001</t>
         </is>
       </c>
       <c r="T38" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DHS_001; IRS_001; EU_001; SNE_001; MOFCOM_002; TSLA_001; EU_002; BIS_001; USMCA_001; CASE_002</t>
+          <t>DHS_001; IRS_001; EU_001; SNE_001; TSLA_001; MOFCOM_002; EU_002; BIS_001; USMCA_001; TRD_001</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -31557,7 +31557,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -31703,7 +31703,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USMCA_001; WB_001; IRS_001; WH_002; WTO_004; DHS_001; CASE_002; EU_003; EU_001; EU_002</t>
+          <t>USMCA_001; WB_001; IRS_001; WTO_004; WH_002; DHS_001; EU_003; CASE_002; EU_001; EU_002</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -31784,7 +31784,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>EU_001; DHS_001; EU_003; SNE_001; IEA_001; CSIS_001; UST_001; IRS_001; TSLA_001; WH_002</t>
+          <t>EU_001; DHS_001; EU_003; SNE_001; UST_001; IEA_001; CSIS_001; IRS_001; TSLA_001; WH_002</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -31827,7 +31827,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>CSIS_001; UST_001; WH_002</t>
+          <t>UST_001; CSIS_001; WH_002</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -31865,7 +31865,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>EU_003; CASE_002; DHS_001; UST_001; TRD_001; SNE_001; IEA_001; ALB_001; WH_002; EU_001</t>
+          <t>EU_003; CASE_002; DHS_001; TRD_001; UST_001; IEA_001; SNE_001; ALB_001; EU_001; WH_002</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -31946,7 +31946,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EU_002; EU_004; DHS_001; EU_001; EU_003; WH_002; SNE_001; MOFCOM_002; ALB_001; IEA_001</t>
+          <t>EU_002; EU_004; DHS_001; EU_001; WH_002; EU_003; IEA_001; ALB_001; IRS_001; SNE_001</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -32074,7 +32074,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.8</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -32089,7 +32089,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.925</v>
+        <v>0.907</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>0.839</v>
+        <v>0.842</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1.874</v>
+        <v>1.888</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -32231,11 +32231,11 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>0.825</v>
+        <v>0.85</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>0.833 / 0.892 / 8</t>
+          <t>0.833 / 0.875 / 8</t>
         </is>
       </c>
     </row>
@@ -32246,11 +32246,11 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>0.948 / 0.943 / 8</t>
+          <t>0.923 / 0.943 / 8</t>
         </is>
       </c>
     </row>
@@ -32261,11 +32261,11 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>0.786</v>
+        <v>0.843</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>0.964 / 0.929 / 14</t>
+          <t>0.964 / 0.938 / 14</t>
         </is>
       </c>
     </row>
@@ -32276,11 +32276,11 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>0.895 / 0.94 / 6</t>
+          <t>0.829 / 0.94 / 6</t>
         </is>
       </c>
     </row>
@@ -32291,11 +32291,11 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>0.771</v>
+        <v>0.8</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>0.948 / 0.883 / 7</t>
+          <t>0.924 / 0.892 / 7</t>
         </is>
       </c>
     </row>
